--- a/Issues Section Template.xlsx
+++ b/Issues Section Template.xlsx
@@ -16,101 +16,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="385">
-  <si>
-    <t>Eco Warriors</t>
-  </si>
-  <si>
-    <t>Unseen Academia</t>
-  </si>
-  <si>
-    <t>Fowl Play</t>
-  </si>
-  <si>
-    <t>Unequal Devolution</t>
-  </si>
-  <si>
-    <t>Liquidity Problems</t>
-  </si>
-  <si>
-    <t>All About the Hustle</t>
-  </si>
-  <si>
-    <t>The Magical Adventures of @LEADER@@</t>
-  </si>
-  <si>
-    <t>A High-Interest Coupnundrum</t>
-  </si>
-  <si>
-    <t>Profitable for Doctrine</t>
-  </si>
-  <si>
-    <t>Hospital Problems Ramping Up</t>
-  </si>
-  <si>
-    <t>Spare the (Plutonium) Rod</t>
-  </si>
-  <si>
-    <t>Loose Lips, Characters Shipped?</t>
-  </si>
-  <si>
-    <t>The Taste of Revenge</t>
-  </si>
-  <si>
-    <t>Don’t Point That Thing at Me!</t>
-  </si>
-  <si>
-    <t>DEMONYM, Interrupted</t>
-  </si>
-  <si>
-    <t>[Sedgistan; ed: Verdant Haven]</t>
-  </si>
-  <si>
-    <t>[Cefalonia; ed: Candlewhisper Archive]</t>
-  </si>
-  <si>
-    <t>[West Barack and East Obama; ed: Baggieland]</t>
-  </si>
-  <si>
-    <t>[Circulationem Pecunia; ed: SherpDaWerp]</t>
-  </si>
-  <si>
-    <t>[Verdant Haven; ed: Candlewhisper Archive]</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="414">
   <si>
     <t>[The Free Joy State; ed: Candlewhisper Archive]</t>
   </si>
   <si>
-    <t>[Kaschovia; ed: Candlewhisper Archive]</t>
-  </si>
-  <si>
-    <t>[Hulldom; ed: Verdant Haven]</t>
-  </si>
-  <si>
-    <t>[Tinhampton; ed: Verdant Haven]</t>
-  </si>
-  <si>
     <t>TBD</t>
   </si>
   <si>
-    <t>[Klaus Devestatorie, ed: Verdany Haven]</t>
-  </si>
-  <si>
-    <t>[Cretox State; ed: Baggieland]</t>
-  </si>
-  <si>
-    <t>[Novo Terres; ed: Pogaria]</t>
-  </si>
-  <si>
-    <t>[Edush; ed: Gnejs]</t>
-  </si>
-  <si>
-    <t>[Mierria; ed: Westinor]</t>
-  </si>
-  <si>
-    <t>[Reploid Productions]</t>
-  </si>
-  <si>
     <t>More Popular Than @@FAITH@@</t>
   </si>
   <si>
@@ -1171,6 +1084,180 @@
   </si>
   <si>
     <t>[Candlewhisper Archive; ed: The Ankhalic Vaspriot]</t>
+  </si>
+  <si>
+    <t>Alcohol is legal</t>
+  </si>
+  <si>
+    <t>Smoking is legal</t>
+  </si>
+  <si>
+    <t>Alcohol is not legal</t>
+  </si>
+  <si>
+    <t>Smoking is not legal</t>
+  </si>
+  <si>
+    <t>To the Letter</t>
+  </si>
+  <si>
+    <t>A Day of Prayer</t>
+  </si>
+  <si>
+    <t>IOU?</t>
+  </si>
+  <si>
+    <t>We Hold These Truths To Be Self-Evident</t>
+  </si>
+  <si>
+    <t>Peace, Love, and @@NAME@@</t>
+  </si>
+  <si>
+    <t>Milk Made</t>
+  </si>
+  <si>
+    <t>Zinc Before You Mint</t>
+  </si>
+  <si>
+    <t>Exemptional Babies</t>
+  </si>
+  <si>
+    <t>@@LEADER@@ to New @@ANIMAL@@ City: Drop Dead?</t>
+  </si>
+  <si>
+    <t>Mommy and Daddy Issues</t>
+  </si>
+  <si>
+    <t>Saving Faith</t>
+  </si>
+  <si>
+    <t>Representative Housework</t>
+  </si>
+  <si>
+    <t>The Three Electioneers</t>
+  </si>
+  <si>
+    <t>Post-Prosecution Demise</t>
+  </si>
+  <si>
+    <t>Virtual Vigilantes</t>
+  </si>
+  <si>
+    <t>Mold, Mold, Go Away</t>
+  </si>
+  <si>
+    <t>@@NAME@@’s Chipping In</t>
+  </si>
+  <si>
+    <t>Fortune Favors the Glitch</t>
+  </si>
+  <si>
+    <t>Liberté, Égalité, Calamité</t>
+  </si>
+  <si>
+    <t>Making Headlines</t>
+  </si>
+  <si>
+    <t>A Chemical Reactionary</t>
+  </si>
+  <si>
+    <t>Sesquipedalianism Not So Supercalifragilisticexpialidocious?</t>
+  </si>
+  <si>
+    <t>The Grandmaster in the Machine</t>
+  </si>
+  <si>
+    <t>Jam to Gram’s Jam</t>
+  </si>
+  <si>
+    <t>Too Coal For School</t>
+  </si>
+  <si>
+    <t>Pennypincher Nation?</t>
+  </si>
+  <si>
+    <t>Disposable Assets</t>
+  </si>
+  <si>
+    <t>Jet Set Regrets</t>
+  </si>
+  <si>
+    <t>A Jolly Killing</t>
+  </si>
+  <si>
+    <t>These Options Are Not An Option</t>
+  </si>
+  <si>
+    <t>Avant-Guard</t>
+  </si>
+  <si>
+    <t>The Sinking of @@CAPITAL@@</t>
+  </si>
+  <si>
+    <t>[The Ankhalic Vaspriot &amp; Thorn1000; ed: The Ankhalic Vaspriot]</t>
+  </si>
+  <si>
+    <t>[Ostrovskiy; ed: Ostrovskiy]</t>
+  </si>
+  <si>
+    <t>[Dexterra; ed: Nardin]</t>
+  </si>
+  <si>
+    <t>[Dushina, Pathonia; ed: Kractero]</t>
+  </si>
+  <si>
+    <t>[Jim the Baptist, Dabarastan; ed: Bisofeyr]</t>
+  </si>
+  <si>
+    <t>[Frieden-und Freudenland; ed: Raionitu &amp; Haymarket Riot]</t>
+  </si>
+  <si>
+    <t>[USS Monitor; ed: Nardin]</t>
+  </si>
+  <si>
+    <t>[Fhaengshia; ed: Haymarket Riot]</t>
+  </si>
+  <si>
+    <t>[Barlyy; ed: Kractero]</t>
+  </si>
+  <si>
+    <t>[Great Kwaan; ed: The Ankhalic Vaspriot]</t>
+  </si>
+  <si>
+    <t>[Aleaterra; ed: Bisofeyr]</t>
+  </si>
+  <si>
+    <t>[Talsien; ed: Southland]</t>
+  </si>
+  <si>
+    <t>[Torkeland; ed: Kractero]</t>
+  </si>
+  <si>
+    <t>[Millenhaal; ed: Millenhaal]</t>
+  </si>
+  <si>
+    <t>[Malatoga; ed: Haymarket Riot]</t>
+  </si>
+  <si>
+    <t>[National Coraland of Fishery; ed: Candlewhisper Archive &amp; Haymarket Riot]</t>
+  </si>
+  <si>
+    <t>[Black Havens; ed: Raionitu]</t>
+  </si>
+  <si>
+    <t>[Novoroyssia; ed: Cretox State &amp; Southland]</t>
+  </si>
+  <si>
+    <t>[Western Balkania; ed: Nardin]</t>
+  </si>
+  <si>
+    <t>[Noahs Second Country; ed: Haymarket Riot]</t>
+  </si>
+  <si>
+    <t>[Kractero &amp; Cat Without Legs; ed: Kractero]</t>
+  </si>
+  <si>
+    <t>[EA Corporations; ed: Southland]</t>
   </si>
 </sst>
 </file>
@@ -1186,12 +1273,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1206,8 +1299,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1502,7 +1596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D187"/>
+  <dimension ref="A1:D270"/>
   <sheetFormatPr defaultColWidth="8.9375" defaultRowHeight="14.35"/>
   <cols>
     <col min="1" max="1" width="9.8203125" customWidth="1"/>
@@ -1516,10 +1610,10 @@
         <v>1581</v>
       </c>
       <c r="B1" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="D1" t="str">
         <f t="shared" ref="D1:D64" si="0">"#"&amp;A1&amp;": [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#"&amp;A1&amp;"]"&amp;B1&amp;"[/url] "&amp;C1</f>
@@ -1531,10 +1625,10 @@
         <v>1588</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="D2" t="str">
         <f t="shared" si="0"/>
@@ -1546,10 +1640,10 @@
         <v>1589</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="D3" t="str">
         <f t="shared" si="0"/>
@@ -1561,10 +1655,10 @@
         <v>1590</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="D4" t="str">
         <f t="shared" si="0"/>
@@ -1576,10 +1670,10 @@
         <v>1591</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="D5" t="str">
         <f t="shared" si="0"/>
@@ -1591,10 +1685,10 @@
         <v>1592</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="D6" t="str">
         <f t="shared" si="0"/>
@@ -1606,10 +1700,10 @@
         <v>1593</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="D7" t="str">
         <f t="shared" si="0"/>
@@ -1621,10 +1715,10 @@
         <v>1594</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D8" t="str">
         <f t="shared" si="0"/>
@@ -1636,10 +1730,10 @@
         <v>1595</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="D9" t="str">
         <f t="shared" si="0"/>
@@ -1651,10 +1745,10 @@
         <v>1596</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D10" t="str">
         <f t="shared" si="0"/>
@@ -1666,10 +1760,10 @@
         <v>1597</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D11" t="str">
         <f t="shared" si="0"/>
@@ -1681,10 +1775,10 @@
         <v>1598</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D12" t="str">
         <f t="shared" si="0"/>
@@ -1696,10 +1790,10 @@
         <v>1599</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="D13" t="str">
         <f t="shared" si="0"/>
@@ -1711,10 +1805,10 @@
         <v>1600</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D14" t="str">
         <f t="shared" si="0"/>
@@ -1726,10 +1820,10 @@
         <v>1601</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="D15" t="str">
         <f t="shared" si="0"/>
@@ -1745,7 +1839,7 @@
         <v>@@NAME@@’s Bark Worse Than Its Byte?</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="D16" t="str">
         <f t="shared" si="0"/>
@@ -1757,10 +1851,10 @@
         <v>1603</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="D17" t="str">
         <f t="shared" si="0"/>
@@ -1772,10 +1866,10 @@
         <v>1604</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="D18" t="str">
         <f t="shared" si="0"/>
@@ -1787,10 +1881,10 @@
         <v>1605</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="D19" t="str">
         <f t="shared" si="0"/>
@@ -1802,10 +1896,10 @@
         <v>1606</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="D20" t="str">
         <f t="shared" si="0"/>
@@ -1817,10 +1911,10 @@
         <v>1607</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="D21" t="str">
         <f t="shared" si="0"/>
@@ -1832,10 +1926,10 @@
         <v>1608</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="D22" t="str">
         <f t="shared" si="0"/>
@@ -1847,10 +1941,10 @@
         <v>1609</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="D23" t="str">
         <f t="shared" si="0"/>
@@ -1862,10 +1956,10 @@
         <v>1610</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="D24" t="str">
         <f t="shared" si="0"/>
@@ -1877,10 +1971,10 @@
         <v>1611</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="D25" t="str">
         <f t="shared" si="0"/>
@@ -1892,10 +1986,10 @@
         <v>1612</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="D26" t="str">
         <f t="shared" si="0"/>
@@ -1907,10 +2001,10 @@
         <v>1613</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="D27" t="str">
         <f t="shared" si="0"/>
@@ -1922,10 +2016,10 @@
         <v>1614</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="D28" t="str">
         <f t="shared" si="0"/>
@@ -1937,10 +2031,10 @@
         <v>1615</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="D29" t="str">
         <f t="shared" si="0"/>
@@ -1952,10 +2046,10 @@
         <v>1616</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="D30" t="str">
         <f t="shared" si="0"/>
@@ -1967,10 +2061,10 @@
         <v>1617</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D31" t="str">
         <f t="shared" si="0"/>
@@ -1982,10 +2076,10 @@
         <v>1618</v>
       </c>
       <c r="B32" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="C32" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="D32" t="str">
         <f t="shared" si="0"/>
@@ -1997,10 +2091,10 @@
         <v>1619</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="D33" t="str">
         <f t="shared" si="0"/>
@@ -2012,10 +2106,10 @@
         <v>1620</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="D34" t="str">
         <f t="shared" si="0"/>
@@ -2027,10 +2121,10 @@
         <v>1621</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="D35" t="str">
         <f t="shared" si="0"/>
@@ -2042,10 +2136,10 @@
         <v>1622</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="D36" t="str">
         <f t="shared" si="0"/>
@@ -2057,10 +2151,10 @@
         <v>1623</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="D37" t="str">
         <f t="shared" si="0"/>
@@ -2072,10 +2166,10 @@
         <v>1624</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="C38" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="D38" t="str">
         <f t="shared" si="0"/>
@@ -2087,10 +2181,10 @@
         <v>1625</v>
       </c>
       <c r="B39" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="D39" t="str">
         <f t="shared" si="0"/>
@@ -2102,10 +2196,10 @@
         <v>1626</v>
       </c>
       <c r="B40" t="s">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="C40" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="D40" t="str">
         <f t="shared" si="0"/>
@@ -2117,10 +2211,10 @@
         <v>1627</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="C41" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="D41" t="str">
         <f t="shared" si="0"/>
@@ -2132,10 +2226,10 @@
         <v>1628</v>
       </c>
       <c r="B42" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="C42" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="D42" t="str">
         <f t="shared" si="0"/>
@@ -2147,10 +2241,10 @@
         <v>1629</v>
       </c>
       <c r="B43" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="C43" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="D43" t="str">
         <f t="shared" si="0"/>
@@ -2162,10 +2256,10 @@
         <v>1630</v>
       </c>
       <c r="B44" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="D44" t="str">
         <f t="shared" si="0"/>
@@ -2177,10 +2271,10 @@
         <v>1631</v>
       </c>
       <c r="B45" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="C45" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="D45" t="str">
         <f t="shared" si="0"/>
@@ -2192,10 +2286,10 @@
         <v>1632</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="C46" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="D46" t="str">
         <f t="shared" si="0"/>
@@ -2207,10 +2301,10 @@
         <v>1633</v>
       </c>
       <c r="B47" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="C47" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="D47" t="str">
         <f t="shared" si="0"/>
@@ -2222,10 +2316,10 @@
         <v>1634</v>
       </c>
       <c r="B48" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="C48" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="D48" t="str">
         <f t="shared" si="0"/>
@@ -2237,10 +2331,10 @@
         <v>1635</v>
       </c>
       <c r="B49" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="C49" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="D49" t="str">
         <f t="shared" si="0"/>
@@ -2252,10 +2346,10 @@
         <v>1570</v>
       </c>
       <c r="B50" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="C50" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="D50" t="str">
         <f t="shared" si="0"/>
@@ -2267,10 +2361,10 @@
         <v>1636</v>
       </c>
       <c r="B51" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="C51" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="D51" t="str">
         <f t="shared" si="0"/>
@@ -2282,10 +2376,10 @@
         <v>1637</v>
       </c>
       <c r="B52" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="C52" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="D52" t="str">
         <f t="shared" si="0"/>
@@ -2297,10 +2391,10 @@
         <v>1638</v>
       </c>
       <c r="B53" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="C53" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="D53" t="str">
         <f t="shared" si="0"/>
@@ -2312,10 +2406,10 @@
         <v>1639</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="C54" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="D54" t="str">
         <f t="shared" si="0"/>
@@ -2327,10 +2421,10 @@
         <v>1640</v>
       </c>
       <c r="B55" t="s">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="C55" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="D55" t="str">
         <f t="shared" si="0"/>
@@ -2342,10 +2436,10 @@
         <v>1641</v>
       </c>
       <c r="B56" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="C56" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="D56" t="str">
         <f t="shared" si="0"/>
@@ -2357,10 +2451,10 @@
         <v>1642</v>
       </c>
       <c r="B57" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="C57" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="D57" t="str">
         <f t="shared" si="0"/>
@@ -2372,10 +2466,10 @@
         <v>1643</v>
       </c>
       <c r="B58" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="C58" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="D58" t="str">
         <f t="shared" si="0"/>
@@ -2387,10 +2481,10 @@
         <v>1644</v>
       </c>
       <c r="B59" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="C59" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="D59" t="str">
         <f t="shared" si="0"/>
@@ -2402,10 +2496,10 @@
         <v>1645</v>
       </c>
       <c r="B60" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="C60" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="D60" t="str">
         <f t="shared" si="0"/>
@@ -2417,10 +2511,10 @@
         <v>1646</v>
       </c>
       <c r="B61" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="C61" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="D61" t="str">
         <f t="shared" si="0"/>
@@ -2432,10 +2526,10 @@
         <v>1647</v>
       </c>
       <c r="B62" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="C62" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="D62" t="str">
         <f t="shared" si="0"/>
@@ -2447,10 +2541,10 @@
         <v>1648</v>
       </c>
       <c r="B63" t="s">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="C63" t="s">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="D63" t="str">
         <f t="shared" si="0"/>
@@ -2462,10 +2556,10 @@
         <v>1649</v>
       </c>
       <c r="B64" t="s">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="C64" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="D64" t="str">
         <f t="shared" si="0"/>
@@ -2477,10 +2571,10 @@
         <v>1650</v>
       </c>
       <c r="B65" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="C65" t="s">
-        <v>151</v>
+        <v>122</v>
       </c>
       <c r="D65" t="str">
         <f t="shared" ref="D65:D128" si="1">"#"&amp;A65&amp;": [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#"&amp;A65&amp;"]"&amp;B65&amp;"[/url] "&amp;C65</f>
@@ -2492,10 +2586,10 @@
         <v>1651</v>
       </c>
       <c r="B66" t="s">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="C66" t="s">
-        <v>153</v>
+        <v>124</v>
       </c>
       <c r="D66" t="str">
         <f t="shared" si="1"/>
@@ -2507,10 +2601,10 @@
         <v>1652</v>
       </c>
       <c r="B67" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="C67" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="D67" t="str">
         <f t="shared" si="1"/>
@@ -2522,10 +2616,10 @@
         <v>1653</v>
       </c>
       <c r="B68" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="C68" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="D68" t="str">
         <f t="shared" si="1"/>
@@ -2537,10 +2631,10 @@
         <v>1654</v>
       </c>
       <c r="B69" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="C69" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="D69" t="str">
         <f t="shared" si="1"/>
@@ -2552,10 +2646,10 @@
         <v>1655</v>
       </c>
       <c r="B70" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="C70" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="D70" t="str">
         <f t="shared" si="1"/>
@@ -2567,10 +2661,10 @@
         <v>1656</v>
       </c>
       <c r="B71" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="C71" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="D71" t="str">
         <f t="shared" si="1"/>
@@ -2582,10 +2676,10 @@
         <v>1657</v>
       </c>
       <c r="B72" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="C72" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="D72" t="str">
         <f t="shared" si="1"/>
@@ -2597,10 +2691,10 @@
         <v>1658</v>
       </c>
       <c r="B73" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="C73" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="D73" t="str">
         <f t="shared" si="1"/>
@@ -2612,10 +2706,10 @@
         <v>1659</v>
       </c>
       <c r="B74" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="C74" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="D74" t="str">
         <f t="shared" si="1"/>
@@ -2627,10 +2721,10 @@
         <v>1660</v>
       </c>
       <c r="B75" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="C75" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="D75" t="str">
         <f t="shared" si="1"/>
@@ -2642,10 +2736,10 @@
         <v>1661</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="C76" t="s">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="D76" t="str">
         <f t="shared" si="1"/>
@@ -2657,10 +2751,10 @@
         <v>1662</v>
       </c>
       <c r="B77" t="s">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="C77" t="s">
-        <v>174</v>
+        <v>145</v>
       </c>
       <c r="D77" t="str">
         <f t="shared" si="1"/>
@@ -2672,10 +2766,10 @@
         <v>1663</v>
       </c>
       <c r="B78" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="C78" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="D78" t="str">
         <f t="shared" si="1"/>
@@ -2687,10 +2781,10 @@
         <v>1664</v>
       </c>
       <c r="B79" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="C79" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="D79" t="str">
         <f t="shared" si="1"/>
@@ -2702,10 +2796,10 @@
         <v>1665</v>
       </c>
       <c r="B80" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="C80" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D80" t="str">
         <f t="shared" si="1"/>
@@ -2717,10 +2811,10 @@
         <v>1666</v>
       </c>
       <c r="B81" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="C81" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="D81" t="str">
         <f t="shared" si="1"/>
@@ -2732,10 +2826,10 @@
         <v>1667</v>
       </c>
       <c r="B82" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="C82" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="D82" t="str">
         <f t="shared" si="1"/>
@@ -2747,10 +2841,10 @@
         <v>1668</v>
       </c>
       <c r="B83" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="C83" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="D83" t="str">
         <f t="shared" si="1"/>
@@ -2762,10 +2856,10 @@
         <v>1669</v>
       </c>
       <c r="B84" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="C84" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="D84" t="str">
         <f t="shared" si="1"/>
@@ -2777,10 +2871,10 @@
         <v>1670</v>
       </c>
       <c r="B85" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="C85" t="s">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D85" t="str">
         <f t="shared" si="1"/>
@@ -2792,10 +2886,10 @@
         <v>1671</v>
       </c>
       <c r="B86" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="C86" t="s">
-        <v>196</v>
+        <v>167</v>
       </c>
       <c r="D86" t="str">
         <f t="shared" si="1"/>
@@ -2807,10 +2901,10 @@
         <v>1672</v>
       </c>
       <c r="B87" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="C87" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="D87" t="str">
         <f t="shared" si="1"/>
@@ -2822,10 +2916,10 @@
         <v>1673</v>
       </c>
       <c r="B88" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="C88" t="s">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="D88" t="str">
         <f t="shared" si="1"/>
@@ -2837,10 +2931,10 @@
         <v>1674</v>
       </c>
       <c r="B89" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="C89" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="D89" t="str">
         <f t="shared" si="1"/>
@@ -2852,10 +2946,10 @@
         <v>1675</v>
       </c>
       <c r="B90" t="s">
-        <v>195</v>
+        <v>166</v>
       </c>
       <c r="C90" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="D90" t="str">
         <f t="shared" si="1"/>
@@ -2867,10 +2961,10 @@
         <v>1676</v>
       </c>
       <c r="B91" t="s">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="C91" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="D91" t="str">
         <f t="shared" si="1"/>
@@ -2882,10 +2976,10 @@
         <v>1677</v>
       </c>
       <c r="B92" t="s">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="C92" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="D92" t="str">
         <f t="shared" si="1"/>
@@ -2897,10 +2991,10 @@
         <v>1678</v>
       </c>
       <c r="B93" t="s">
-        <v>203</v>
+        <v>174</v>
       </c>
       <c r="C93" t="s">
-        <v>221</v>
+        <v>192</v>
       </c>
       <c r="D93" t="str">
         <f t="shared" si="1"/>
@@ -2912,10 +3006,10 @@
         <v>1679</v>
       </c>
       <c r="B94" t="s">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="C94" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="D94" t="str">
         <f t="shared" si="1"/>
@@ -2927,10 +3021,10 @@
         <v>1680</v>
       </c>
       <c r="B95" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="C95" t="s">
-        <v>217</v>
+        <v>188</v>
       </c>
       <c r="D95" t="str">
         <f t="shared" si="1"/>
@@ -2942,10 +3036,10 @@
         <v>1681</v>
       </c>
       <c r="B96" t="s">
-        <v>216</v>
+        <v>187</v>
       </c>
       <c r="C96" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="D96" t="str">
         <f t="shared" si="1"/>
@@ -2957,10 +3051,10 @@
         <v>1682</v>
       </c>
       <c r="B97" t="s">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="C97" t="s">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="D97" t="str">
         <f t="shared" si="1"/>
@@ -2972,10 +3066,10 @@
         <v>1683</v>
       </c>
       <c r="B98" t="s">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="C98" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="D98" t="str">
         <f t="shared" si="1"/>
@@ -2987,10 +3081,10 @@
         <v>1684</v>
       </c>
       <c r="B99" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="C99" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="D99" t="str">
         <f t="shared" si="1"/>
@@ -3002,10 +3096,10 @@
         <v>1685</v>
       </c>
       <c r="B100" t="s">
-        <v>209</v>
+        <v>180</v>
       </c>
       <c r="C100" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="D100" t="str">
         <f t="shared" si="1"/>
@@ -3017,10 +3111,10 @@
         <v>1686</v>
       </c>
       <c r="B101" t="s">
-        <v>210</v>
+        <v>181</v>
       </c>
       <c r="C101" t="s">
-        <v>227</v>
+        <v>198</v>
       </c>
       <c r="D101" t="str">
         <f t="shared" si="1"/>
@@ -3032,10 +3126,10 @@
         <v>1687</v>
       </c>
       <c r="B102" t="s">
-        <v>211</v>
+        <v>182</v>
       </c>
       <c r="C102" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="D102" t="str">
         <f t="shared" si="1"/>
@@ -3047,10 +3141,10 @@
         <v>1688</v>
       </c>
       <c r="B103" t="s">
-        <v>212</v>
+        <v>183</v>
       </c>
       <c r="C103" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="D103" t="str">
         <f t="shared" si="1"/>
@@ -3062,10 +3156,10 @@
         <v>1689</v>
       </c>
       <c r="B104" t="s">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="C104" t="s">
-        <v>229</v>
+        <v>200</v>
       </c>
       <c r="D104" t="str">
         <f t="shared" si="1"/>
@@ -3077,10 +3171,10 @@
         <v>1690</v>
       </c>
       <c r="B105" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="C105" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="D105" t="str">
         <f t="shared" si="1"/>
@@ -3092,10 +3186,10 @@
         <v>1691</v>
       </c>
       <c r="B106" t="s">
-        <v>215</v>
+        <v>186</v>
       </c>
       <c r="C106" t="s">
-        <v>231</v>
+        <v>202</v>
       </c>
       <c r="D106" t="str">
         <f t="shared" si="1"/>
@@ -3107,10 +3201,10 @@
         <v>1692</v>
       </c>
       <c r="B107" t="s">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c r="C107" t="s">
-        <v>233</v>
+        <v>204</v>
       </c>
       <c r="D107" t="str">
         <f t="shared" si="1"/>
@@ -3122,10 +3216,10 @@
         <v>1693</v>
       </c>
       <c r="B108" t="s">
-        <v>234</v>
+        <v>205</v>
       </c>
       <c r="C108" t="s">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="D108" t="str">
         <f t="shared" si="1"/>
@@ -3137,10 +3231,10 @@
         <v>1694</v>
       </c>
       <c r="B109" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="C109" t="s">
-        <v>237</v>
+        <v>208</v>
       </c>
       <c r="D109" t="str">
         <f t="shared" si="1"/>
@@ -3152,10 +3246,10 @@
         <v>1695</v>
       </c>
       <c r="B110" t="s">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="C110" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="D110" t="str">
         <f t="shared" si="1"/>
@@ -3167,10 +3261,10 @@
         <v>1696</v>
       </c>
       <c r="B111" t="s">
-        <v>240</v>
+        <v>211</v>
       </c>
       <c r="C111" t="s">
-        <v>241</v>
+        <v>212</v>
       </c>
       <c r="D111" t="str">
         <f t="shared" si="1"/>
@@ -3182,10 +3276,10 @@
         <v>1697</v>
       </c>
       <c r="B112" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="C112" t="s">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="D112" t="str">
         <f t="shared" si="1"/>
@@ -3197,10 +3291,10 @@
         <v>1698</v>
       </c>
       <c r="B113" t="s">
-        <v>244</v>
+        <v>215</v>
       </c>
       <c r="C113" t="s">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="D113" t="str">
         <f t="shared" si="1"/>
@@ -3212,10 +3306,10 @@
         <v>1699</v>
       </c>
       <c r="B114" t="s">
-        <v>246</v>
+        <v>217</v>
       </c>
       <c r="C114" t="s">
-        <v>247</v>
+        <v>218</v>
       </c>
       <c r="D114" t="str">
         <f t="shared" si="1"/>
@@ -3227,10 +3321,10 @@
         <v>1700</v>
       </c>
       <c r="B115" t="s">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="C115" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="D115" t="str">
         <f t="shared" si="1"/>
@@ -3242,10 +3336,10 @@
         <v>1701</v>
       </c>
       <c r="B116" t="s">
-        <v>249</v>
+        <v>220</v>
       </c>
       <c r="C116" t="s">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="D116" t="str">
         <f t="shared" si="1"/>
@@ -3257,10 +3351,10 @@
         <v>1702</v>
       </c>
       <c r="B117" t="s">
-        <v>251</v>
+        <v>222</v>
       </c>
       <c r="C117" t="s">
-        <v>252</v>
+        <v>223</v>
       </c>
       <c r="D117" t="str">
         <f t="shared" si="1"/>
@@ -3272,10 +3366,10 @@
         <v>1703</v>
       </c>
       <c r="B118" t="s">
-        <v>253</v>
+        <v>224</v>
       </c>
       <c r="C118" t="s">
-        <v>254</v>
+        <v>225</v>
       </c>
       <c r="D118" t="str">
         <f t="shared" si="1"/>
@@ -3287,10 +3381,10 @@
         <v>1704</v>
       </c>
       <c r="B119" t="s">
-        <v>255</v>
+        <v>226</v>
       </c>
       <c r="C119" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="D119" t="str">
         <f t="shared" si="1"/>
@@ -3302,10 +3396,10 @@
         <v>1705</v>
       </c>
       <c r="B120" t="s">
-        <v>257</v>
+        <v>228</v>
       </c>
       <c r="C120" t="s">
-        <v>258</v>
+        <v>229</v>
       </c>
       <c r="D120" t="str">
         <f t="shared" si="1"/>
@@ -3317,10 +3411,10 @@
         <v>1706</v>
       </c>
       <c r="B121" t="s">
-        <v>259</v>
+        <v>230</v>
       </c>
       <c r="C121" t="s">
-        <v>260</v>
+        <v>231</v>
       </c>
       <c r="D121" t="str">
         <f t="shared" si="1"/>
@@ -3332,10 +3426,10 @@
         <v>1707</v>
       </c>
       <c r="B122" t="s">
-        <v>261</v>
+        <v>232</v>
       </c>
       <c r="C122" t="s">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="D122" t="str">
         <f t="shared" si="1"/>
@@ -3347,10 +3441,10 @@
         <v>1708</v>
       </c>
       <c r="B123" t="s">
-        <v>263</v>
+        <v>234</v>
       </c>
       <c r="C123" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="D123" t="str">
         <f t="shared" si="1"/>
@@ -3362,10 +3456,10 @@
         <v>1709</v>
       </c>
       <c r="B124" t="s">
-        <v>265</v>
+        <v>236</v>
       </c>
       <c r="C124" t="s">
-        <v>266</v>
+        <v>237</v>
       </c>
       <c r="D124" t="str">
         <f t="shared" si="1"/>
@@ -3377,10 +3471,10 @@
         <v>1710</v>
       </c>
       <c r="B125" t="s">
-        <v>267</v>
+        <v>238</v>
       </c>
       <c r="C125" t="s">
-        <v>268</v>
+        <v>239</v>
       </c>
       <c r="D125" t="str">
         <f t="shared" si="1"/>
@@ -3392,10 +3486,10 @@
         <v>1711</v>
       </c>
       <c r="B126" t="s">
-        <v>272</v>
+        <v>243</v>
       </c>
       <c r="C126" t="s">
-        <v>269</v>
+        <v>240</v>
       </c>
       <c r="D126" t="str">
         <f t="shared" si="1"/>
@@ -3407,10 +3501,10 @@
         <v>1712</v>
       </c>
       <c r="B127" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="C127" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="D127" t="str">
         <f t="shared" si="1"/>
@@ -3422,10 +3516,10 @@
         <v>1713</v>
       </c>
       <c r="B128" t="s">
-        <v>277</v>
+        <v>248</v>
       </c>
       <c r="C128" t="s">
-        <v>301</v>
+        <v>272</v>
       </c>
       <c r="D128" t="str">
         <f t="shared" si="1"/>
@@ -3437,13 +3531,13 @@
         <v>1714</v>
       </c>
       <c r="B129" t="s">
-        <v>273</v>
+        <v>244</v>
       </c>
       <c r="C129" t="s">
-        <v>273</v>
+        <v>244</v>
       </c>
       <c r="D129" t="str">
-        <f t="shared" ref="D129:D187" si="2">"#"&amp;A129&amp;": [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#"&amp;A129&amp;"]"&amp;B129&amp;"[/url] "&amp;C129</f>
+        <f t="shared" ref="D129:D192" si="2">"#"&amp;A129&amp;": [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#"&amp;A129&amp;"]"&amp;B129&amp;"[/url] "&amp;C129</f>
         <v>#1714: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1714][Republik Hintonia; ed: Baggieland][/url] [Republik Hintonia; ed: Baggieland]</v>
       </c>
     </row>
@@ -3452,10 +3546,10 @@
         <v>1715</v>
       </c>
       <c r="B130" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="C130" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="D130" t="str">
         <f t="shared" si="2"/>
@@ -3467,10 +3561,10 @@
         <v>1716</v>
       </c>
       <c r="B131" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="C131" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="D131" t="str">
         <f t="shared" si="2"/>
@@ -3482,10 +3576,10 @@
         <v>1717</v>
       </c>
       <c r="B132" t="s">
-        <v>278</v>
+        <v>249</v>
       </c>
       <c r="C132" t="s">
-        <v>302</v>
+        <v>273</v>
       </c>
       <c r="D132" t="str">
         <f t="shared" si="2"/>
@@ -3497,10 +3591,10 @@
         <v>1718</v>
       </c>
       <c r="B133" t="s">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="C133" t="s">
-        <v>303</v>
+        <v>274</v>
       </c>
       <c r="D133" t="str">
         <f t="shared" si="2"/>
@@ -3512,10 +3606,10 @@
         <v>1719</v>
       </c>
       <c r="B134" t="s">
-        <v>280</v>
+        <v>251</v>
       </c>
       <c r="C134" t="s">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="D134" t="str">
         <f t="shared" si="2"/>
@@ -3527,10 +3621,10 @@
         <v>1720</v>
       </c>
       <c r="B135" t="s">
-        <v>281</v>
+        <v>252</v>
       </c>
       <c r="C135" t="s">
-        <v>305</v>
+        <v>276</v>
       </c>
       <c r="D135" t="str">
         <f t="shared" si="2"/>
@@ -3542,10 +3636,10 @@
         <v>1721</v>
       </c>
       <c r="B136" t="s">
-        <v>282</v>
+        <v>253</v>
       </c>
       <c r="C136" t="s">
-        <v>306</v>
+        <v>277</v>
       </c>
       <c r="D136" t="str">
         <f t="shared" si="2"/>
@@ -3557,10 +3651,10 @@
         <v>1722</v>
       </c>
       <c r="B137" t="s">
-        <v>283</v>
+        <v>254</v>
       </c>
       <c r="C137" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="D137" t="str">
         <f t="shared" si="2"/>
@@ -3572,10 +3666,10 @@
         <v>1723</v>
       </c>
       <c r="B138" t="s">
-        <v>284</v>
+        <v>255</v>
       </c>
       <c r="C138" t="s">
-        <v>307</v>
+        <v>278</v>
       </c>
       <c r="D138" t="str">
         <f t="shared" si="2"/>
@@ -3587,10 +3681,10 @@
         <v>1724</v>
       </c>
       <c r="B139" t="s">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="C139" t="s">
-        <v>308</v>
+        <v>279</v>
       </c>
       <c r="D139" t="str">
         <f t="shared" si="2"/>
@@ -3602,10 +3696,10 @@
         <v>1725</v>
       </c>
       <c r="B140" t="s">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="C140" t="s">
-        <v>309</v>
+        <v>280</v>
       </c>
       <c r="D140" t="str">
         <f t="shared" si="2"/>
@@ -3617,10 +3711,10 @@
         <v>1726</v>
       </c>
       <c r="B141" t="s">
-        <v>287</v>
+        <v>258</v>
       </c>
       <c r="C141" t="s">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="D141" t="str">
         <f t="shared" si="2"/>
@@ -3632,10 +3726,10 @@
         <v>1727</v>
       </c>
       <c r="B142" t="s">
-        <v>288</v>
+        <v>259</v>
       </c>
       <c r="C142" t="s">
-        <v>311</v>
+        <v>282</v>
       </c>
       <c r="D142" t="str">
         <f t="shared" si="2"/>
@@ -3647,10 +3741,10 @@
         <v>1728</v>
       </c>
       <c r="B143" t="s">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="C143" t="s">
-        <v>312</v>
+        <v>283</v>
       </c>
       <c r="D143" t="str">
         <f t="shared" si="2"/>
@@ -3662,10 +3756,10 @@
         <v>1729</v>
       </c>
       <c r="B144" t="s">
-        <v>290</v>
+        <v>261</v>
       </c>
       <c r="C144" t="s">
-        <v>313</v>
+        <v>284</v>
       </c>
       <c r="D144" t="str">
         <f t="shared" si="2"/>
@@ -3677,10 +3771,10 @@
         <v>1730</v>
       </c>
       <c r="B145" t="s">
-        <v>291</v>
+        <v>262</v>
       </c>
       <c r="C145" t="s">
-        <v>314</v>
+        <v>285</v>
       </c>
       <c r="D145" t="str">
         <f t="shared" si="2"/>
@@ -3692,10 +3786,10 @@
         <v>1731</v>
       </c>
       <c r="B146" t="s">
-        <v>276</v>
+        <v>247</v>
       </c>
       <c r="C146" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="D146" t="str">
         <f t="shared" si="2"/>
@@ -3707,10 +3801,10 @@
         <v>1732</v>
       </c>
       <c r="B147" t="s">
-        <v>292</v>
+        <v>263</v>
       </c>
       <c r="C147" t="s">
-        <v>315</v>
+        <v>286</v>
       </c>
       <c r="D147" t="str">
         <f t="shared" si="2"/>
@@ -3722,10 +3816,10 @@
         <v>1733</v>
       </c>
       <c r="B148" t="s">
-        <v>293</v>
+        <v>264</v>
       </c>
       <c r="C148" t="s">
-        <v>316</v>
+        <v>287</v>
       </c>
       <c r="D148" t="str">
         <f t="shared" si="2"/>
@@ -3737,10 +3831,10 @@
         <v>1734</v>
       </c>
       <c r="B149" t="s">
-        <v>294</v>
+        <v>265</v>
       </c>
       <c r="C149" t="s">
-        <v>317</v>
+        <v>288</v>
       </c>
       <c r="D149" t="str">
         <f t="shared" si="2"/>
@@ -3752,10 +3846,10 @@
         <v>1735</v>
       </c>
       <c r="B150" t="s">
-        <v>295</v>
+        <v>266</v>
       </c>
       <c r="C150" t="s">
-        <v>318</v>
+        <v>289</v>
       </c>
       <c r="D150" t="str">
         <f t="shared" si="2"/>
@@ -3767,10 +3861,10 @@
         <v>1736</v>
       </c>
       <c r="B151" t="s">
-        <v>296</v>
+        <v>267</v>
       </c>
       <c r="C151" t="s">
-        <v>319</v>
+        <v>290</v>
       </c>
       <c r="D151" t="str">
         <f t="shared" si="2"/>
@@ -3782,10 +3876,10 @@
         <v>1737</v>
       </c>
       <c r="B152" t="s">
-        <v>297</v>
+        <v>268</v>
       </c>
       <c r="C152" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="D152" t="str">
         <f t="shared" si="2"/>
@@ -3797,10 +3891,10 @@
         <v>1738</v>
       </c>
       <c r="B153" t="s">
-        <v>298</v>
+        <v>269</v>
       </c>
       <c r="C153" t="s">
-        <v>320</v>
+        <v>291</v>
       </c>
       <c r="D153" t="str">
         <f t="shared" si="2"/>
@@ -3812,10 +3906,10 @@
         <v>1739</v>
       </c>
       <c r="B154" t="s">
-        <v>299</v>
+        <v>270</v>
       </c>
       <c r="C154" t="s">
-        <v>321</v>
+        <v>292</v>
       </c>
       <c r="D154" t="str">
         <f t="shared" si="2"/>
@@ -3827,10 +3921,10 @@
         <v>1740</v>
       </c>
       <c r="B155" t="s">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="C155" t="s">
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="D155" t="str">
         <f t="shared" si="2"/>
@@ -3842,10 +3936,10 @@
         <v>1741</v>
       </c>
       <c r="B156" t="s">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="C156" t="s">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="D156" t="str">
         <f t="shared" si="2"/>
@@ -3857,10 +3951,10 @@
         <v>1742</v>
       </c>
       <c r="B157" t="s">
-        <v>324</v>
+        <v>295</v>
       </c>
       <c r="C157" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="D157" t="str">
         <f t="shared" si="2"/>
@@ -3872,10 +3966,10 @@
         <v>1743</v>
       </c>
       <c r="B158" t="s">
-        <v>325</v>
+        <v>296</v>
       </c>
       <c r="C158" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="D158" t="str">
         <f t="shared" si="2"/>
@@ -3887,10 +3981,10 @@
         <v>1744</v>
       </c>
       <c r="B159" t="s">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="C159" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="D159" t="str">
         <f t="shared" si="2"/>
@@ -3902,10 +3996,10 @@
         <v>1745</v>
       </c>
       <c r="B160" t="s">
-        <v>327</v>
+        <v>298</v>
       </c>
       <c r="C160" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="D160" t="str">
         <f t="shared" si="2"/>
@@ -3917,10 +4011,10 @@
         <v>1746</v>
       </c>
       <c r="B161" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="C161" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="D161" t="str">
         <f t="shared" si="2"/>
@@ -3932,10 +4026,10 @@
         <v>1747</v>
       </c>
       <c r="B162" t="s">
-        <v>329</v>
+        <v>300</v>
       </c>
       <c r="C162" t="s">
-        <v>361</v>
+        <v>332</v>
       </c>
       <c r="D162" t="str">
         <f t="shared" si="2"/>
@@ -3947,10 +4041,10 @@
         <v>1748</v>
       </c>
       <c r="B163" t="s">
-        <v>330</v>
+        <v>301</v>
       </c>
       <c r="C163" t="s">
-        <v>362</v>
+        <v>333</v>
       </c>
       <c r="D163" t="str">
         <f t="shared" si="2"/>
@@ -3962,10 +4056,10 @@
         <v>1749</v>
       </c>
       <c r="B164" t="s">
-        <v>331</v>
+        <v>302</v>
       </c>
       <c r="C164" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="D164" t="str">
         <f t="shared" si="2"/>
@@ -3977,10 +4071,10 @@
         <v>1750</v>
       </c>
       <c r="B165" t="s">
-        <v>332</v>
+        <v>303</v>
       </c>
       <c r="C165" t="s">
-        <v>364</v>
+        <v>335</v>
       </c>
       <c r="D165" t="str">
         <f t="shared" si="2"/>
@@ -3992,10 +4086,10 @@
         <v>1751</v>
       </c>
       <c r="B166" t="s">
-        <v>333</v>
+        <v>304</v>
       </c>
       <c r="C166" t="s">
-        <v>365</v>
+        <v>336</v>
       </c>
       <c r="D166" t="str">
         <f t="shared" si="2"/>
@@ -4007,10 +4101,10 @@
         <v>1752</v>
       </c>
       <c r="B167" t="s">
-        <v>334</v>
+        <v>305</v>
       </c>
       <c r="C167" t="s">
-        <v>366</v>
+        <v>337</v>
       </c>
       <c r="D167" t="str">
         <f t="shared" si="2"/>
@@ -4022,10 +4116,10 @@
         <v>1753</v>
       </c>
       <c r="B168" t="s">
-        <v>335</v>
+        <v>306</v>
       </c>
       <c r="C168" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="D168" t="str">
         <f t="shared" si="2"/>
@@ -4037,10 +4131,10 @@
         <v>1754</v>
       </c>
       <c r="B169" t="s">
-        <v>336</v>
+        <v>307</v>
       </c>
       <c r="C169" t="s">
-        <v>368</v>
+        <v>339</v>
       </c>
       <c r="D169" t="str">
         <f t="shared" si="2"/>
@@ -4052,10 +4146,10 @@
         <v>1755</v>
       </c>
       <c r="B170" t="s">
-        <v>337</v>
+        <v>308</v>
       </c>
       <c r="C170" t="s">
-        <v>368</v>
+        <v>339</v>
       </c>
       <c r="D170" t="str">
         <f t="shared" si="2"/>
@@ -4067,10 +4161,10 @@
         <v>1756</v>
       </c>
       <c r="B171" t="s">
-        <v>338</v>
+        <v>309</v>
       </c>
       <c r="C171" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="D171" t="str">
         <f t="shared" si="2"/>
@@ -4082,10 +4176,10 @@
         <v>1757</v>
       </c>
       <c r="B172" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="C172" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="D172" t="str">
         <f t="shared" si="2"/>
@@ -4097,10 +4191,10 @@
         <v>1758</v>
       </c>
       <c r="B173" t="s">
-        <v>340</v>
+        <v>311</v>
       </c>
       <c r="C173" t="s">
-        <v>371</v>
+        <v>342</v>
       </c>
       <c r="D173" t="str">
         <f t="shared" si="2"/>
@@ -4112,10 +4206,10 @@
         <v>1759</v>
       </c>
       <c r="B174" t="s">
-        <v>341</v>
+        <v>312</v>
       </c>
       <c r="C174" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="D174" t="str">
         <f t="shared" si="2"/>
@@ -4127,10 +4221,10 @@
         <v>1760</v>
       </c>
       <c r="B175" t="s">
-        <v>342</v>
+        <v>313</v>
       </c>
       <c r="C175" t="s">
-        <v>373</v>
+        <v>344</v>
       </c>
       <c r="D175" t="str">
         <f t="shared" si="2"/>
@@ -4142,10 +4236,10 @@
         <v>1761</v>
       </c>
       <c r="B176" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="C176" t="s">
-        <v>374</v>
+        <v>345</v>
       </c>
       <c r="D176" t="str">
         <f t="shared" si="2"/>
@@ -4157,10 +4251,10 @@
         <v>1762</v>
       </c>
       <c r="B177" t="s">
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="C177" t="s">
-        <v>252</v>
+        <v>223</v>
       </c>
       <c r="D177" t="str">
         <f t="shared" si="2"/>
@@ -4172,10 +4266,10 @@
         <v>1763</v>
       </c>
       <c r="B178" t="s">
-        <v>345</v>
+        <v>316</v>
       </c>
       <c r="C178" t="s">
-        <v>375</v>
+        <v>346</v>
       </c>
       <c r="D178" t="str">
         <f t="shared" si="2"/>
@@ -4187,10 +4281,10 @@
         <v>1764</v>
       </c>
       <c r="B179" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="C179" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
       <c r="D179" t="str">
         <f t="shared" si="2"/>
@@ -4202,10 +4296,10 @@
         <v>1765</v>
       </c>
       <c r="B180" t="s">
-        <v>347</v>
+        <v>318</v>
       </c>
       <c r="C180" t="s">
-        <v>377</v>
+        <v>348</v>
       </c>
       <c r="D180" t="str">
         <f t="shared" si="2"/>
@@ -4217,10 +4311,10 @@
         <v>1766</v>
       </c>
       <c r="B181" t="s">
-        <v>348</v>
+        <v>319</v>
       </c>
       <c r="C181" t="s">
-        <v>378</v>
+        <v>349</v>
       </c>
       <c r="D181" t="str">
         <f t="shared" si="2"/>
@@ -4232,10 +4326,10 @@
         <v>1767</v>
       </c>
       <c r="B182" t="s">
-        <v>349</v>
+        <v>320</v>
       </c>
       <c r="C182" t="s">
-        <v>379</v>
+        <v>350</v>
       </c>
       <c r="D182" t="str">
         <f t="shared" si="2"/>
@@ -4247,10 +4341,10 @@
         <v>1768</v>
       </c>
       <c r="B183" t="s">
-        <v>350</v>
+        <v>321</v>
       </c>
       <c r="C183" t="s">
-        <v>380</v>
+        <v>351</v>
       </c>
       <c r="D183" t="str">
         <f t="shared" si="2"/>
@@ -4262,10 +4356,10 @@
         <v>1769</v>
       </c>
       <c r="B184" t="s">
-        <v>351</v>
+        <v>322</v>
       </c>
       <c r="C184" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="D184" t="str">
         <f t="shared" si="2"/>
@@ -4277,10 +4371,10 @@
         <v>1770</v>
       </c>
       <c r="B185" t="s">
-        <v>352</v>
+        <v>323</v>
       </c>
       <c r="C185" t="s">
-        <v>382</v>
+        <v>353</v>
       </c>
       <c r="D185" t="str">
         <f t="shared" si="2"/>
@@ -4292,10 +4386,10 @@
         <v>1771</v>
       </c>
       <c r="B186" t="s">
-        <v>353</v>
+        <v>324</v>
       </c>
       <c r="C186" t="s">
-        <v>383</v>
+        <v>354</v>
       </c>
       <c r="D186" t="str">
         <f t="shared" si="2"/>
@@ -4307,14 +4401,766 @@
         <v>1772</v>
       </c>
       <c r="B187" t="s">
-        <v>354</v>
+        <v>325</v>
       </c>
       <c r="C187" t="s">
+        <v>355</v>
+      </c>
+      <c r="D187" t="str">
+        <f t="shared" si="2"/>
+        <v>#1772: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1772]Spare Any Change?[/url] [Candlewhisper Archive; ed: The Ankhalic Vaspriot]</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188" s="1">
+        <v>1773</v>
+      </c>
+      <c r="B188" t="s">
+        <v>360</v>
+      </c>
+      <c r="C188" t="s">
+        <v>392</v>
+      </c>
+      <c r="D188" t="str">
+        <f t="shared" si="2"/>
+        <v>#1773: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1773]To the Letter[/url] [The Ankhalic Vaspriot &amp; Thorn1000; ed: The Ankhalic Vaspriot]</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189">
+        <v>1774</v>
+      </c>
+      <c r="B189" t="s">
+        <v>361</v>
+      </c>
+      <c r="C189" t="s">
+        <v>191</v>
+      </c>
+      <c r="D189" t="str">
+        <f t="shared" si="2"/>
+        <v>#1774: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1774]A Day of Prayer[/url] [Raionitu; ed: Raionitu]</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190">
+        <v>1775</v>
+      </c>
+      <c r="B190" t="s">
+        <v>362</v>
+      </c>
+      <c r="C190" t="s">
+        <v>212</v>
+      </c>
+      <c r="D190" t="str">
+        <f t="shared" si="2"/>
+        <v>#1775: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1775]IOU?[/url] [Candlewhisper Archive; ed: Klaus Devestatorie]</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191">
+        <v>1776</v>
+      </c>
+      <c r="B191" t="s">
+        <v>363</v>
+      </c>
+      <c r="C191" t="s">
+        <v>393</v>
+      </c>
+      <c r="D191" t="str">
+        <f t="shared" si="2"/>
+        <v>#1776: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1776]We Hold These Truths To Be Self-Evident[/url] [Ostrovskiy; ed: Ostrovskiy]</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
+      <c r="A192">
+        <v>1777</v>
+      </c>
+      <c r="B192" t="s">
+        <v>364</v>
+      </c>
+      <c r="C192" t="s">
+        <v>394</v>
+      </c>
+      <c r="D192" t="str">
+        <f t="shared" si="2"/>
+        <v>#1777: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1777]Peace, Love, and @@NAME@@[/url] [Dexterra; ed: Nardin]</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="A193">
+        <v>1778</v>
+      </c>
+      <c r="B193" t="s">
+        <v>365</v>
+      </c>
+      <c r="C193" t="s">
+        <v>223</v>
+      </c>
+      <c r="D193" t="str">
+        <f t="shared" ref="D193:D221" si="3">"#"&amp;A193&amp;": [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#"&amp;A193&amp;"]"&amp;B193&amp;"[/url] "&amp;C193</f>
+        <v>#1778: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1778]Milk Made[/url] [Candlewhisper Archive; ed: Bisofeyr]</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194">
+        <v>1779</v>
+      </c>
+      <c r="B194" t="s">
+        <v>366</v>
+      </c>
+      <c r="C194" t="s">
+        <v>395</v>
+      </c>
+      <c r="D194" t="str">
+        <f t="shared" si="3"/>
+        <v>#1779: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1779]Zinc Before You Mint[/url] [Dushina, Pathonia; ed: Kractero]</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195">
+        <v>1780</v>
+      </c>
+      <c r="B195" t="s">
+        <v>367</v>
+      </c>
+      <c r="C195" t="s">
+        <v>396</v>
+      </c>
+      <c r="D195" t="str">
+        <f t="shared" si="3"/>
+        <v>#1780: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1780]Exemptional Babies[/url] [Jim the Baptist, Dabarastan; ed: Bisofeyr]</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196">
+        <v>1781</v>
+      </c>
+      <c r="B196" t="s">
+        <v>368</v>
+      </c>
+      <c r="C196" t="s">
+        <v>275</v>
+      </c>
+      <c r="D196" t="str">
+        <f t="shared" si="3"/>
+        <v>#1781: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1781]@@LEADER@@ to New @@ANIMAL@@ City: Drop Dead?[/url] [Southland; ed: Southland]</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197">
+        <v>1782</v>
+      </c>
+      <c r="B197" t="s">
+        <v>369</v>
+      </c>
+      <c r="C197" t="s">
+        <v>397</v>
+      </c>
+      <c r="D197" t="str">
+        <f t="shared" si="3"/>
+        <v>#1782: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1782]Mommy and Daddy Issues[/url] [Frieden-und Freudenland; ed: Raionitu &amp; Haymarket Riot]</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198">
+        <v>1783</v>
+      </c>
+      <c r="B198" t="s">
+        <v>370</v>
+      </c>
+      <c r="C198" t="s">
+        <v>398</v>
+      </c>
+      <c r="D198" t="str">
+        <f t="shared" si="3"/>
+        <v>#1783: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1783]Saving Faith[/url] [USS Monitor; ed: Nardin]</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199">
+        <v>1784</v>
+      </c>
+      <c r="B199" t="s">
+        <v>371</v>
+      </c>
+      <c r="C199" t="s">
+        <v>399</v>
+      </c>
+      <c r="D199" t="str">
+        <f t="shared" si="3"/>
+        <v>#1784: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1784]Representative Housework[/url] [Fhaengshia; ed: Haymarket Riot]</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200">
+        <v>1785</v>
+      </c>
+      <c r="B200" t="s">
+        <v>372</v>
+      </c>
+      <c r="C200" t="s">
+        <v>293</v>
+      </c>
+      <c r="D200" t="str">
+        <f t="shared" si="3"/>
+        <v>#1785: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1785]The Three Electioneers[/url] [Bisofeyr; ed: Bisofeyr]</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201">
+        <v>1786</v>
+      </c>
+      <c r="B201" t="s">
+        <v>336</v>
+      </c>
+      <c r="C201" t="s">
+        <v>336</v>
+      </c>
+      <c r="D201" t="str">
+        <f t="shared" si="3"/>
+        <v>#1786: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1786][Haymarket Riot; ed: Haymarket Riot][/url] [Haymarket Riot; ed: Haymarket Riot]</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202">
+        <v>1787</v>
+      </c>
+      <c r="B202" t="s">
+        <v>373</v>
+      </c>
+      <c r="C202" t="s">
+        <v>400</v>
+      </c>
+      <c r="D202" t="str">
+        <f t="shared" si="3"/>
+        <v>#1787: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1787]Post-Prosecution Demise[/url] [Barlyy; ed: Kractero]</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203">
+        <v>1788</v>
+      </c>
+      <c r="B203" t="s">
+        <v>374</v>
+      </c>
+      <c r="C203" t="s">
+        <v>401</v>
+      </c>
+      <c r="D203" t="str">
+        <f t="shared" si="3"/>
+        <v>#1788: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1788]Virtual Vigilantes[/url] [Great Kwaan; ed: The Ankhalic Vaspriot]</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204">
+        <v>1789</v>
+      </c>
+      <c r="B204" t="s">
+        <v>375</v>
+      </c>
+      <c r="C204" t="s">
+        <v>402</v>
+      </c>
+      <c r="D204" t="str">
+        <f t="shared" si="3"/>
+        <v>#1789: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1789]Mold, Mold, Go Away[/url] [Aleaterra; ed: Bisofeyr]</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205">
+        <v>1790</v>
+      </c>
+      <c r="B205" t="s">
+        <v>376</v>
+      </c>
+      <c r="C205" t="s">
+        <v>403</v>
+      </c>
+      <c r="D205" t="str">
+        <f t="shared" si="3"/>
+        <v>#1790: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1790]@@NAME@@’s Chipping In[/url] [Talsien; ed: Southland]</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206">
+        <v>1791</v>
+      </c>
+      <c r="B206" t="s">
+        <v>377</v>
+      </c>
+      <c r="C206" t="s">
+        <v>404</v>
+      </c>
+      <c r="D206" t="str">
+        <f t="shared" si="3"/>
+        <v>#1791: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1791]Fortune Favors the Glitch[/url] [Torkeland; ed: Kractero]</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207">
+        <v>1792</v>
+      </c>
+      <c r="B207" t="s">
+        <v>378</v>
+      </c>
+      <c r="C207" t="s">
+        <v>405</v>
+      </c>
+      <c r="D207" t="str">
+        <f t="shared" si="3"/>
+        <v>#1792: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1792]Liberté, Égalité, Calamité[/url] [Millenhaal; ed: Millenhaal]</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208">
+        <v>1793</v>
+      </c>
+      <c r="B208" t="s">
+        <v>379</v>
+      </c>
+      <c r="C208" t="s">
+        <v>171</v>
+      </c>
+      <c r="D208" t="str">
+        <f t="shared" si="3"/>
+        <v>#1793: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1793]Making Headlines[/url] [The Ankhalic Vaspriot; ed: The Ankhalic Vaspriot]</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209">
+        <v>1794</v>
+      </c>
+      <c r="B209" t="s">
+        <v>380</v>
+      </c>
+      <c r="C209" t="s">
+        <v>336</v>
+      </c>
+      <c r="D209" t="str">
+        <f t="shared" si="3"/>
+        <v>#1794: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1794]A Chemical Reactionary[/url] [Haymarket Riot; ed: Haymarket Riot]</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210">
+        <v>1795</v>
+      </c>
+      <c r="B210" t="s">
+        <v>381</v>
+      </c>
+      <c r="C210" t="s">
+        <v>280</v>
+      </c>
+      <c r="D210" t="str">
+        <f t="shared" si="3"/>
+        <v>#1795: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1795]Sesquipedalianism Not So Supercalifragilisticexpialidocious?[/url] [The Realizer; ed: The Ankhalic Vaspriot]</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211">
+        <v>1796</v>
+      </c>
+      <c r="B211" t="s">
+        <v>382</v>
+      </c>
+      <c r="C211" t="s">
+        <v>169</v>
+      </c>
+      <c r="D211" t="str">
+        <f t="shared" si="3"/>
+        <v>#1796: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1796]The Grandmaster in the Machine[/url] [Klaus Devestatorie; ed: Klaus Devestatorie]</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212">
+        <v>1797</v>
+      </c>
+      <c r="B212" t="s">
+        <v>383</v>
+      </c>
+      <c r="C212" t="s">
+        <v>406</v>
+      </c>
+      <c r="D212" t="str">
+        <f t="shared" si="3"/>
+        <v>#1797: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1797]Jam to Gram’s Jam[/url] [Malatoga; ed: Haymarket Riot]</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213">
+        <v>1798</v>
+      </c>
+      <c r="B213" t="s">
         <v>384</v>
       </c>
-      <c r="D187" t="str">
-        <f t="shared" si="2"/>
-        <v>#1772: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1772]Spare Any Change?[/url] [Candlewhisper Archive; ed: The Ankhalic Vaspriot]</v>
+      <c r="C213" t="s">
+        <v>407</v>
+      </c>
+      <c r="D213" t="str">
+        <f t="shared" si="3"/>
+        <v>#1798: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1798]Too Coal For School[/url] [National Coraland of Fishery; ed: Candlewhisper Archive &amp; Haymarket Riot]</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214">
+        <v>1799</v>
+      </c>
+      <c r="B214" t="s">
+        <v>385</v>
+      </c>
+      <c r="C214" t="s">
+        <v>408</v>
+      </c>
+      <c r="D214" t="str">
+        <f t="shared" si="3"/>
+        <v>#1799: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1799]Pennypincher Nation?[/url] [Black Havens; ed: Raionitu]</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215">
+        <v>1800</v>
+      </c>
+      <c r="B215" t="s">
+        <v>386</v>
+      </c>
+      <c r="C215" t="s">
+        <v>223</v>
+      </c>
+      <c r="D215" t="str">
+        <f t="shared" si="3"/>
+        <v>#1800: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1800]Disposable Assets[/url] [Candlewhisper Archive; ed: Bisofeyr]</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216">
+        <v>1801</v>
+      </c>
+      <c r="B216" t="s">
+        <v>387</v>
+      </c>
+      <c r="C216" t="s">
+        <v>409</v>
+      </c>
+      <c r="D216" t="str">
+        <f t="shared" si="3"/>
+        <v>#1801: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1801]Jet Set Regrets[/url] [Novoroyssia; ed: Cretox State &amp; Southland]</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217">
+        <v>1802</v>
+      </c>
+      <c r="B217" t="s">
+        <v>388</v>
+      </c>
+      <c r="C217" t="s">
+        <v>410</v>
+      </c>
+      <c r="D217" t="str">
+        <f t="shared" si="3"/>
+        <v>#1802: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1802]A Jolly Killing[/url] [Western Balkania; ed: Nardin]</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218">
+        <v>1803</v>
+      </c>
+      <c r="B218" t="s">
+        <v>389</v>
+      </c>
+      <c r="C218" t="s">
+        <v>411</v>
+      </c>
+      <c r="D218" t="str">
+        <f t="shared" si="3"/>
+        <v>#1803: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1803]These Options Are Not An Option[/url] [Noahs Second Country; ed: Haymarket Riot]</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219">
+        <v>1804</v>
+      </c>
+      <c r="B219" t="s">
+        <v>1</v>
+      </c>
+      <c r="D219" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">#1804: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1804]TBD[/url] </v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220">
+        <v>1805</v>
+      </c>
+      <c r="B220" t="s">
+        <v>390</v>
+      </c>
+      <c r="C220" t="s">
+        <v>412</v>
+      </c>
+      <c r="D220" t="str">
+        <f t="shared" si="3"/>
+        <v>#1805: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1805]Avant-Guard[/url] [Kractero &amp; Cat Without Legs; ed: Kractero]</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221">
+        <v>1806</v>
+      </c>
+      <c r="B221" t="s">
+        <v>391</v>
+      </c>
+      <c r="C221" t="s">
+        <v>413</v>
+      </c>
+      <c r="D221" t="str">
+        <f t="shared" si="3"/>
+        <v>#1806: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1806]The Sinking of @@CAPITAL@@[/url] [EA Corporations; ed: Southland]</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270">
+        <v>1855</v>
       </c>
     </row>
   </sheetData>
@@ -4328,138 +5174,59 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="8.9375" defaultRowHeight="14.35"/>
   <cols>
-    <col min="1" max="2" width="95.703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.703125" customWidth="1"/>
+    <col min="2" max="2" width="39.87890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>357</v>
+      </c>
+      <c r="C1" t="str">
+        <f>"[color=blue]"&amp;A1&amp;"[/color], "&amp;"[color=blue]"&amp;B1&amp;"[/color]"</f>
+        <v>[color=blue]Alcohol is legal[/color], [color=blue]Smoking is legal[/color]</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>358</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>357</v>
+      </c>
+      <c r="C2" t="str">
+        <f>"[color=red]"&amp;A2&amp;"[/color], "&amp;"[color=blue]"&amp;B2&amp;"[/color]"</f>
+        <v>[color=red]Alcohol is not legal[/color], [color=blue]Smoking is legal[/color]</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>356</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>359</v>
+      </c>
+      <c r="C3" t="str">
+        <f>"[color=blue]"&amp;A3&amp;"[/color], "&amp;"[color=red]"&amp;B3&amp;"[/color]"</f>
+        <v>[color=blue]Alcohol is legal[/color], [color=red]Smoking is not legal[/color]</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>358</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
+        <v>359</v>
+      </c>
+      <c r="C4" t="str">
+        <f>"[color=red]"&amp;A4&amp;"[/color], "&amp;"[color=red]"&amp;B4&amp;"[/color]"</f>
+        <v>[color=red]Alcohol is not legal[/color], [color=red]Smoking is not legal[/color]</v>
       </c>
     </row>
   </sheetData>
@@ -4477,130 +5244,130 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="B1" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="B2" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>203</v>
+        <v>174</v>
       </c>
       <c r="B3" t="s">
-        <v>221</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="B4" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="B5" t="s">
-        <v>217</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>216</v>
+        <v>187</v>
       </c>
       <c r="B6" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="B7" t="s">
-        <v>223</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="B8" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="B9" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>209</v>
+        <v>180</v>
       </c>
       <c r="B10" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>210</v>
+        <v>181</v>
       </c>
       <c r="B11" t="s">
-        <v>227</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>211</v>
+        <v>182</v>
       </c>
       <c r="B12" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>212</v>
+        <v>183</v>
       </c>
       <c r="B13" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="B14" t="s">
-        <v>229</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>215</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s">
-        <v>231</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/Issues Section Template.xlsx
+++ b/Issues Section Template.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="462">
   <si>
     <t>[The Free Joy State; ed: Candlewhisper Archive]</t>
   </si>
@@ -1258,6 +1258,150 @@
   </si>
   <si>
     <t>[EA Corporations; ed: Southland]</t>
+  </si>
+  <si>
+    <t>Ethicist’s Edict</t>
+  </si>
+  <si>
+    <t>Mann and Boy</t>
+  </si>
+  <si>
+    <t>Origin Story</t>
+  </si>
+  <si>
+    <t>An Issue of Magnetude</t>
+  </si>
+  <si>
+    <t>Too Busy to Handle</t>
+  </si>
+  <si>
+    <t>An Unequal Union</t>
+  </si>
+  <si>
+    <t>Junk the Junk</t>
+  </si>
+  <si>
+    <t>Rock the Vote</t>
+  </si>
+  <si>
+    <t>Seed Sovereignty</t>
+  </si>
+  <si>
+    <t>Raise the Unsinkable?</t>
+  </si>
+  <si>
+    <t>A Bitter Pill to Swallow</t>
+  </si>
+  <si>
+    <t>Private Parts</t>
+  </si>
+  <si>
+    <t>I Came, I Thaw, I Conquered</t>
+  </si>
+  <si>
+    <t>Whatever Happened to Saturday Night?</t>
+  </si>
+  <si>
+    <t>A Dilemma of (Musical) Note</t>
+  </si>
+  <si>
+    <t>ShortTok on the Clock</t>
+  </si>
+  <si>
+    <t>High Stakes In the Jungle</t>
+  </si>
+  <si>
+    <t>A Great Swansong?</t>
+  </si>
+  <si>
+    <t>Fish Out of Water</t>
+  </si>
+  <si>
+    <t>Cyclist? More Like Cycle-Pest!</t>
+  </si>
+  <si>
+    <t>Row, Row, Row Your Drug Boat!</t>
+  </si>
+  <si>
+    <t>A Dole-ful Gamble</t>
+  </si>
+  <si>
+    <t>Fly on the Wall Diplomacy</t>
+  </si>
+  <si>
+    <t>You Wouldn’t Download Segregation</t>
+  </si>
+  <si>
+    <t>Some @@DEMONYM_NOUN_PLURAL@@ May Die</t>
+  </si>
+  <si>
+    <t>À La Cartel</t>
+  </si>
+  <si>
+    <t>Patron Sinner</t>
+  </si>
+  <si>
+    <t>[The Free Joy State; ed: The Free Joy State, Raionitu]</t>
+  </si>
+  <si>
+    <t>[Unogonduria; ed: Kractero]</t>
+  </si>
+  <si>
+    <t>[Le Libertia; ed: Noahs Second Country, The Ankhalic Vaspriot]</t>
+  </si>
+  <si>
+    <t>[Geolapo; ed: Haymarket Riot, Jiangbei]</t>
+  </si>
+  <si>
+    <t>[Fhaengshia; ed: Ostrovskiy]</t>
+  </si>
+  <si>
+    <t>[Kractero; ed: Kractero]</t>
+  </si>
+  <si>
+    <t>[Chan Island; ed: Haymarket Riot]</t>
+  </si>
+  <si>
+    <t>[Greater Earth Ecovillage Network; ed: Raionitu]</t>
+  </si>
+  <si>
+    <t>[Carpathina; ed: Haymarket Riot]</t>
+  </si>
+  <si>
+    <t>[Thorn1000; ed: Kaschovia]</t>
+  </si>
+  <si>
+    <t>[Colmis; ed: Bisofeyr]</t>
+  </si>
+  <si>
+    <t>[Haymarket Riot, Sapphica Sororitas; ed: Haymarket Riot]</t>
+  </si>
+  <si>
+    <t>[Starenia; ed: The Ankhalic Vaspriot]</t>
+  </si>
+  <si>
+    <t>[The Northern Glacial Borderlands; ed: Southland]</t>
+  </si>
+  <si>
+    <t>[Northern Slatavia; ed: Ostrovskiy]</t>
+  </si>
+  <si>
+    <t>[Chan Island; ed: Southland]</t>
+  </si>
+  <si>
+    <t>[Westinor; ed: Southland]</t>
+  </si>
+  <si>
+    <t>[Markanite; ed: The Ankhalic Vaspriot]</t>
+  </si>
+  <si>
+    <t>[Burg Land; ed: Kractero]</t>
+  </si>
+  <si>
+    <t>[Giovanniland; ed: Kractero]</t>
+  </si>
+  <si>
+    <t>[The Free Joy State; ed: Nardin]</t>
   </si>
 </sst>
 </file>
@@ -1304,7 +1448,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1312,9 +1456,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Larissa-Design">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Larissa">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1352,7 +1496,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Larissa">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1422,7 +1566,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Larissa">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1597,7 +1741,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D270"/>
-  <sheetFormatPr defaultColWidth="8.9375" defaultRowHeight="14.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.9375" defaultRowHeight="14.35"/>
   <cols>
     <col min="1" max="1" width="9.8203125" customWidth="1"/>
     <col min="2" max="2" width="32.76171875" customWidth="1"/>
@@ -4497,7 +4641,7 @@
         <v>223</v>
       </c>
       <c r="D193" t="str">
-        <f t="shared" ref="D193:D221" si="3">"#"&amp;A193&amp;": [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#"&amp;A193&amp;"]"&amp;B193&amp;"[/url] "&amp;C193</f>
+        <f t="shared" ref="D193:D248" si="3">"#"&amp;A193&amp;": [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#"&amp;A193&amp;"]"&amp;B193&amp;"[/url] "&amp;C193</f>
         <v>#1778: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1778]Milk Made[/url] [Candlewhisper Archive; ed: Bisofeyr]</v>
       </c>
     </row>
@@ -4922,173 +5066,443 @@
       <c r="A222">
         <v>1807</v>
       </c>
+      <c r="B222" t="s">
+        <v>414</v>
+      </c>
+      <c r="C222" t="s">
+        <v>293</v>
+      </c>
+      <c r="D222" t="str">
+        <f t="shared" si="3"/>
+        <v>#1807: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1807]Ethicist’s Edict[/url] [Bisofeyr; ed: Bisofeyr]</v>
+      </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223">
         <v>1808</v>
       </c>
+      <c r="B223" t="s">
+        <v>415</v>
+      </c>
+      <c r="C223" t="s">
+        <v>441</v>
+      </c>
+      <c r="D223" t="str">
+        <f t="shared" si="3"/>
+        <v>#1808: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1808]Mann and Boy[/url] [The Free Joy State; ed: The Free Joy State, Raionitu]</v>
+      </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224">
         <v>1809</v>
       </c>
-    </row>
-    <row r="225" spans="1:1">
+      <c r="B224" t="s">
+        <v>416</v>
+      </c>
+      <c r="C224" t="s">
+        <v>442</v>
+      </c>
+      <c r="D224" t="str">
+        <f t="shared" si="3"/>
+        <v>#1809: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1809]Origin Story[/url] [Unogonduria; ed: Kractero]</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
       <c r="A225">
         <v>1810</v>
       </c>
-    </row>
-    <row r="226" spans="1:1">
+      <c r="B225" t="s">
+        <v>417</v>
+      </c>
+      <c r="C225" t="s">
+        <v>443</v>
+      </c>
+      <c r="D225" t="str">
+        <f t="shared" si="3"/>
+        <v>#1810: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1810]An Issue of Magnetude[/url] [Le Libertia; ed: Noahs Second Country, The Ankhalic Vaspriot]</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
       <c r="A226">
         <v>1811</v>
       </c>
-    </row>
-    <row r="227" spans="1:1">
+      <c r="B226" t="s">
+        <v>418</v>
+      </c>
+      <c r="C226" t="s">
+        <v>444</v>
+      </c>
+      <c r="D226" t="str">
+        <f t="shared" si="3"/>
+        <v>#1811: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1811]Too Busy to Handle[/url] [Geolapo; ed: Haymarket Riot, Jiangbei]</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
       <c r="A227">
         <v>1812</v>
       </c>
-    </row>
-    <row r="228" spans="1:1">
+      <c r="B227" t="s">
+        <v>419</v>
+      </c>
+      <c r="C227" t="s">
+        <v>445</v>
+      </c>
+      <c r="D227" t="str">
+        <f t="shared" si="3"/>
+        <v>#1812: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1812]An Unequal Union[/url] [Fhaengshia; ed: Ostrovskiy]</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
       <c r="A228">
         <v>1813</v>
       </c>
-    </row>
-    <row r="229" spans="1:1">
+      <c r="B228" t="s">
+        <v>420</v>
+      </c>
+      <c r="C228" t="s">
+        <v>446</v>
+      </c>
+      <c r="D228" t="str">
+        <f t="shared" si="3"/>
+        <v>#1813: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1813]Junk the Junk[/url] [Kractero; ed: Kractero]</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
       <c r="A229">
         <v>1814</v>
       </c>
-    </row>
-    <row r="230" spans="1:1">
+      <c r="B229" t="s">
+        <v>421</v>
+      </c>
+      <c r="C229" t="s">
+        <v>447</v>
+      </c>
+      <c r="D229" t="str">
+        <f t="shared" si="3"/>
+        <v>#1814: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1814]Rock the Vote[/url] [Chan Island; ed: Haymarket Riot]</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
       <c r="A230">
         <v>1815</v>
       </c>
-    </row>
-    <row r="231" spans="1:1">
+      <c r="B230" t="s">
+        <v>422</v>
+      </c>
+      <c r="C230" t="s">
+        <v>448</v>
+      </c>
+      <c r="D230" t="str">
+        <f t="shared" si="3"/>
+        <v>#1815: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1815]Seed Sovereignty[/url] [Greater Earth Ecovillage Network; ed: Raionitu]</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
       <c r="A231">
         <v>1816</v>
       </c>
-    </row>
-    <row r="232" spans="1:1">
+      <c r="B231" t="s">
+        <v>423</v>
+      </c>
+      <c r="C231" t="s">
+        <v>449</v>
+      </c>
+      <c r="D231" t="str">
+        <f t="shared" si="3"/>
+        <v>#1816: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1816]Raise the Unsinkable?[/url] [Carpathina; ed: Haymarket Riot]</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
       <c r="A232">
         <v>1817</v>
       </c>
-    </row>
-    <row r="233" spans="1:1">
+      <c r="B232" t="s">
+        <v>424</v>
+      </c>
+      <c r="C232" t="s">
+        <v>450</v>
+      </c>
+      <c r="D232" t="str">
+        <f t="shared" si="3"/>
+        <v>#1817: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1817]A Bitter Pill to Swallow[/url] [Thorn1000; ed: Kaschovia]</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
       <c r="A233">
         <v>1818</v>
       </c>
-    </row>
-    <row r="234" spans="1:1">
+      <c r="B233" t="s">
+        <v>425</v>
+      </c>
+      <c r="C233" t="s">
+        <v>223</v>
+      </c>
+      <c r="D233" t="str">
+        <f t="shared" si="3"/>
+        <v>#1818: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1818]Private Parts[/url] [Candlewhisper Archive; ed: Bisofeyr]</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
       <c r="A234">
         <v>1819</v>
       </c>
-    </row>
-    <row r="235" spans="1:1">
+      <c r="B234" t="s">
+        <v>426</v>
+      </c>
+      <c r="C234" t="s">
+        <v>451</v>
+      </c>
+      <c r="D234" t="str">
+        <f t="shared" si="3"/>
+        <v>#1819: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1819]I Came, I Thaw, I Conquered[/url] [Colmis; ed: Bisofeyr]</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
       <c r="A235">
         <v>1820</v>
       </c>
-    </row>
-    <row r="236" spans="1:1">
+      <c r="B235" t="s">
+        <v>427</v>
+      </c>
+      <c r="C235" t="s">
+        <v>452</v>
+      </c>
+      <c r="D235" t="str">
+        <f t="shared" si="3"/>
+        <v>#1820: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1820]Whatever Happened to Saturday Night?[/url] [Haymarket Riot, Sapphica Sororitas; ed: Haymarket Riot]</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
       <c r="A236">
         <v>1821</v>
       </c>
-    </row>
-    <row r="237" spans="1:1">
+      <c r="B236" t="s">
+        <v>428</v>
+      </c>
+      <c r="C236" t="s">
+        <v>453</v>
+      </c>
+      <c r="D236" t="str">
+        <f t="shared" si="3"/>
+        <v>#1821: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1821]A Dilemma of (Musical) Note[/url] [Starenia; ed: The Ankhalic Vaspriot]</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
       <c r="A237">
         <v>1822</v>
       </c>
-    </row>
-    <row r="238" spans="1:1">
+      <c r="B237" t="s">
+        <v>429</v>
+      </c>
+      <c r="C237" t="s">
+        <v>454</v>
+      </c>
+      <c r="D237" t="str">
+        <f t="shared" si="3"/>
+        <v>#1822: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1822]ShortTok on the Clock[/url] [The Northern Glacial Borderlands; ed: Southland]</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
       <c r="A238">
         <v>1823</v>
       </c>
-    </row>
-    <row r="239" spans="1:1">
+      <c r="B238" t="s">
+        <v>430</v>
+      </c>
+      <c r="C238" t="s">
+        <v>455</v>
+      </c>
+      <c r="D238" t="str">
+        <f t="shared" si="3"/>
+        <v>#1823: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1823]High Stakes In the Jungle[/url] [Northern Slatavia; ed: Ostrovskiy]</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
       <c r="A239">
         <v>1824</v>
       </c>
-    </row>
-    <row r="240" spans="1:1">
+      <c r="B239" t="s">
+        <v>431</v>
+      </c>
+      <c r="C239" t="s">
+        <v>456</v>
+      </c>
+      <c r="D239" t="str">
+        <f t="shared" si="3"/>
+        <v>#1824: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1824]A Great Swansong?[/url] [Chan Island; ed: Southland]</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
       <c r="A240">
         <v>1825</v>
       </c>
-    </row>
-    <row r="241" spans="1:1">
+      <c r="B240" t="s">
+        <v>432</v>
+      </c>
+      <c r="C240" t="s">
+        <v>457</v>
+      </c>
+      <c r="D240" t="str">
+        <f t="shared" si="3"/>
+        <v>#1825: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1825]Fish Out of Water[/url] [Westinor; ed: Southland]</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
       <c r="A241">
         <v>1826</v>
       </c>
-    </row>
-    <row r="242" spans="1:1">
+      <c r="B241" t="s">
+        <v>433</v>
+      </c>
+      <c r="C241" t="s">
+        <v>458</v>
+      </c>
+      <c r="D241" t="str">
+        <f t="shared" si="3"/>
+        <v>#1826: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1826]Cyclist? More Like Cycle-Pest![/url] [Markanite; ed: The Ankhalic Vaspriot]</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
       <c r="A242">
         <v>1827</v>
       </c>
-    </row>
-    <row r="243" spans="1:1">
+      <c r="B242" t="s">
+        <v>434</v>
+      </c>
+      <c r="C242" t="s">
+        <v>459</v>
+      </c>
+      <c r="D242" t="str">
+        <f t="shared" si="3"/>
+        <v>#1827: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1827]Row, Row, Row Your Drug Boat![/url] [Burg Land; ed: Kractero]</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
       <c r="A243">
         <v>1828</v>
       </c>
-    </row>
-    <row r="244" spans="1:1">
+      <c r="B243" t="s">
+        <v>435</v>
+      </c>
+      <c r="C243" t="s">
+        <v>460</v>
+      </c>
+      <c r="D243" t="str">
+        <f t="shared" si="3"/>
+        <v>#1828: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1828]A Dole-ful Gamble[/url] [Giovanniland; ed: Kractero]</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
       <c r="A244">
         <v>1829</v>
       </c>
-    </row>
-    <row r="245" spans="1:1">
+      <c r="B244" t="s">
+        <v>436</v>
+      </c>
+      <c r="C244" t="s">
+        <v>399</v>
+      </c>
+      <c r="D244" t="str">
+        <f t="shared" si="3"/>
+        <v>#1829: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1829]Fly on the Wall Diplomacy[/url] [Fhaengshia; ed: Haymarket Riot]</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
       <c r="A245">
         <v>1830</v>
       </c>
-    </row>
-    <row r="246" spans="1:1">
+      <c r="B245" t="s">
+        <v>437</v>
+      </c>
+      <c r="C245" t="s">
+        <v>191</v>
+      </c>
+      <c r="D245" t="str">
+        <f t="shared" si="3"/>
+        <v>#1830: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1830]You Wouldn’t Download Segregation[/url] [Raionitu; ed: Raionitu]</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
       <c r="A246">
         <v>1831</v>
       </c>
-    </row>
-    <row r="247" spans="1:1">
+      <c r="B246" t="s">
+        <v>438</v>
+      </c>
+      <c r="C246" t="s">
+        <v>336</v>
+      </c>
+      <c r="D246" t="str">
+        <f t="shared" si="3"/>
+        <v>#1831: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1831]Some @@DEMONYM_NOUN_PLURAL@@ May Die[/url] [Haymarket Riot; ed: Haymarket Riot]</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
       <c r="A247">
         <v>1832</v>
       </c>
-    </row>
-    <row r="248" spans="1:1">
+      <c r="B247" t="s">
+        <v>439</v>
+      </c>
+      <c r="C247" t="s">
+        <v>171</v>
+      </c>
+      <c r="D247" t="str">
+        <f t="shared" si="3"/>
+        <v>#1832: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1832]À La Cartel[/url] [The Ankhalic Vaspriot; ed: The Ankhalic Vaspriot]</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
       <c r="A248">
         <v>1833</v>
       </c>
-    </row>
-    <row r="249" spans="1:1">
+      <c r="B248" t="s">
+        <v>440</v>
+      </c>
+      <c r="C248" t="s">
+        <v>461</v>
+      </c>
+      <c r="D248" t="str">
+        <f t="shared" si="3"/>
+        <v>#1833: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1833]Patron Sinner[/url] [The Free Joy State; ed: Nardin]</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
       <c r="A249">
         <v>1834</v>
       </c>
     </row>
-    <row r="250" spans="1:1">
+    <row r="250" spans="1:4">
       <c r="A250">
         <v>1835</v>
       </c>
     </row>
-    <row r="251" spans="1:1">
+    <row r="251" spans="1:4">
       <c r="A251">
         <v>1836</v>
       </c>
     </row>
-    <row r="252" spans="1:1">
+    <row r="252" spans="1:4">
       <c r="A252">
         <v>1837</v>
       </c>
     </row>
-    <row r="253" spans="1:1">
+    <row r="253" spans="1:4">
       <c r="A253">
         <v>1838</v>
       </c>
     </row>
-    <row r="254" spans="1:1">
+    <row r="254" spans="1:4">
       <c r="A254">
         <v>1839</v>
       </c>
     </row>
-    <row r="255" spans="1:1">
+    <row r="255" spans="1:4">
       <c r="A255">
         <v>1840</v>
       </c>
     </row>
-    <row r="256" spans="1:1">
+    <row r="256" spans="1:4">
       <c r="A256">
         <v>1841</v>
       </c>
@@ -5175,7 +5589,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.9375" defaultRowHeight="14.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.9375" defaultRowHeight="14.35"/>
   <cols>
     <col min="1" max="1" width="44.703125" customWidth="1"/>
     <col min="2" max="2" width="39.87890625" customWidth="1"/>
@@ -5237,7 +5651,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.9375" defaultRowHeight="14.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.9375" defaultRowHeight="14.35"/>
   <cols>
     <col min="1" max="1" width="72.87890625" bestFit="1" customWidth="1"/>
   </cols>

--- a/Issues Section Template.xlsx
+++ b/Issues Section Template.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="472">
   <si>
     <t>[The Free Joy State; ed: Candlewhisper Archive]</t>
   </si>
@@ -1402,6 +1402,36 @@
   </si>
   <si>
     <t>[The Free Joy State; ed: Nardin]</t>
+  </si>
+  <si>
+    <t>Trams-phobic</t>
+  </si>
+  <si>
+    <t>Potatoes in Hot Water</t>
+  </si>
+  <si>
+    <t>Tummy Troubles</t>
+  </si>
+  <si>
+    <t>Sue That Storm</t>
+  </si>
+  <si>
+    <t>Who’s Afraid of Red, Yellow, and Blue?</t>
+  </si>
+  <si>
+    <t>[Lavrada; ed: Haymarket Riot &amp; Southland]</t>
+  </si>
+  <si>
+    <t>[Stevist Guam; ed: Kaschovia]</t>
+  </si>
+  <si>
+    <t>[Buceroque; ed: Nardin]</t>
+  </si>
+  <si>
+    <t>[Roman Garcia; ed: Raionitu]</t>
+  </si>
+  <si>
+    <t>[The Ankhalic Vaspriot; ed: Jiangbei]</t>
   </si>
 </sst>
 </file>
@@ -4641,7 +4671,7 @@
         <v>223</v>
       </c>
       <c r="D193" t="str">
-        <f t="shared" ref="D193:D248" si="3">"#"&amp;A193&amp;": [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#"&amp;A193&amp;"]"&amp;B193&amp;"[/url] "&amp;C193</f>
+        <f t="shared" ref="D193:D253" si="3">"#"&amp;A193&amp;": [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#"&amp;A193&amp;"]"&amp;B193&amp;"[/url] "&amp;C193</f>
         <v>#1778: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1778]Milk Made[/url] [Candlewhisper Archive; ed: Bisofeyr]</v>
       </c>
     </row>
@@ -5471,25 +5501,75 @@
       <c r="A249">
         <v>1834</v>
       </c>
+      <c r="B249" t="s">
+        <v>462</v>
+      </c>
+      <c r="C249" t="s">
+        <v>467</v>
+      </c>
+      <c r="D249" t="str">
+        <f t="shared" si="3"/>
+        <v>#1834: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1834]Trams-phobic[/url] [Lavrada; ed: Haymarket Riot &amp; Southland]</v>
+      </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250">
         <v>1835</v>
       </c>
+      <c r="B250" t="s">
+        <v>463</v>
+      </c>
+      <c r="C250" t="s">
+        <v>468</v>
+      </c>
+      <c r="D250" t="str">
+        <f t="shared" si="3"/>
+        <v>#1835: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1835]Potatoes in Hot Water[/url] [Stevist Guam; ed: Kaschovia]</v>
+      </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251">
         <v>1836</v>
       </c>
+      <c r="B251" t="s">
+        <v>464</v>
+      </c>
+      <c r="C251" t="s">
+        <v>469</v>
+      </c>
+      <c r="D251" t="str">
+        <f t="shared" si="3"/>
+        <v>#1836: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1836]Tummy Troubles[/url] [Buceroque; ed: Nardin]</v>
+      </c>
     </row>
     <row r="252" spans="1:4">
       <c r="A252">
         <v>1837</v>
       </c>
+      <c r="B252" t="s">
+        <v>465</v>
+      </c>
+      <c r="C252" t="s">
+        <v>470</v>
+      </c>
+      <c r="D252" t="str">
+        <f t="shared" si="3"/>
+        <v>#1837: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1837]Sue That Storm[/url] [Roman Garcia; ed: Raionitu]</v>
+      </c>
     </row>
     <row r="253" spans="1:4">
       <c r="A253">
         <v>1838</v>
+      </c>
+      <c r="B253" t="s">
+        <v>466</v>
+      </c>
+      <c r="C253" t="s">
+        <v>471</v>
+      </c>
+      <c r="D253" t="str">
+        <f t="shared" si="3"/>
+        <v>#1838: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1838]Who’s Afraid of Red, Yellow, and Blue?[/url] [The Ankhalic Vaspriot; ed: Jiangbei]</v>
       </c>
     </row>
     <row r="254" spans="1:4">

--- a/Issues Section Template.xlsx
+++ b/Issues Section Template.xlsx
@@ -10,13 +10,14 @@
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
     <sheet name="Blad2" sheetId="2" r:id="rId2"/>
     <sheet name="Blad3" sheetId="3" r:id="rId3"/>
+    <sheet name="Tabelle1" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="125725" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="502">
   <si>
     <t>[The Free Joy State; ed: Candlewhisper Archive]</t>
   </si>
@@ -1432,6 +1433,96 @@
   </si>
   <si>
     <t>[The Ankhalic Vaspriot; ed: Jiangbei]</t>
+  </si>
+  <si>
+    <t>[b][anchor=1839]#1839[/anchor]: Bare the Builder [United Calanworie; ed: Kractero][/b]</t>
+  </si>
+  <si>
+    <t>[b][anchor=1840]#1840[/anchor]: About Face [Candlewhisper Archive; ed: Haymarket Riot][/b]</t>
+  </si>
+  <si>
+    <t>The Issue</t>
+  </si>
+  <si>
+    <t>Appalled by your recent endorsement of intensive farming techniques in pastoral agriculture, yet another group of animal rights activists are now chirping and clucking their tongues about “beak trimming”, a common process in industrial chicken farming used to prevent the birds from pecking each other to death in close quarters. @@NAME@@’s ravenous demand for chicken snack-packs has warranted the use of such inhumane practices.</t>
+  </si>
+  <si>
+    <t>The Debate</t>
+  </si>
+  <si>
+    <t>1. “This isn’t like cutting nails or hair, this so-called trimming involves burning into living tissue with hot blades and scorching heat beams, all without any anaesthetic!” rants Tia Fullippy, dabbing her eyes with a tie-dye organic hemp hankie. “You are tacitly endorsing this awful practice by refusing to condemn intensive farming! Look at these photos of pus-covered and infected beak stumps! Look at them! Now, change your mind, @@LEADER@@! Ban beak trimming, ban caged chicken farming, no matter how much you love your nuggies!”</t>
+  </si>
+  <si>
+    <t>2. “Is it kind to leave chickens able to peck and mutilate each other? Is it kind to cull caged hen populations that wouldn’t be sustainable without strategic medical intervention?” asks veteran farmer Chuck N. Lucken as he pats you on the shoulder. “Of course not, this is the most cost-efficient way to farm one of the tastiest meat animals, and it’s not our fault that our people are fueled by the taste of flesh. Don’t worry about chicken welfare, worry about human welfare! In fact, you ought to be subsidizing my chicken farms, as I’m undertaking a public service here! After all, gotta make more snack-packs no matter the ethical cost, amirite pal?”</t>
+  </si>
+  <si>
+    <t>3. “I think we can have cage farming while still avoiding beak trimming,” mumbles one of your ministers with a full mouth, demonstrating not only that @@HE@@ has cake, but can eat it too. “Hmm, delicious, it’s the fresh eggs that make it so good. Anyway, install some blue-light lamps, genetically select for non-aggressive breeds with small brains that can’t even comprehend their suffering, use pine tar sprays so the chickens don’t taste as good to each other... all of these techniques are alternatives to reducing pecking. Mandate that some combination of these must be used instead of trimming, and everyone can be happy, especially the blissed-out chickens!”</t>
+  </si>
+  <si>
+    <t>[hr][/hr]</t>
+  </si>
+  <si>
+    <t>[b][anchor=1841]#1841[/anchor]: The God Illusion [Varanius; ed: Haymarket Riot][/b]</t>
+  </si>
+  <si>
+    <t>In a stunning episode of impromptu investigative journalism, a plucky band of four random freaks has shocked @@NAME@@ by revealing that Warlock of Aus, divinely-inspired shaman who thousands across @@NAME@@ spent their livelihoods to consult, is a fraud. His supposed communion with the divine was nothing but machinery and parlor tricks. The yellow bricks on his roads were made not of gold, but of urine, as a cost-saving measure. The ragtag team stands before you despite the raging windstorm that has otherwise shutdown @@CAPITAL@@.</t>
+  </si>
+  <si>
+    <t>1. “What punishment could ever be enough for such a wicked man?” cries Borothy Ornament, self-appointed leader of the group who is as drab as a concrete slab made in a beige lab. “I knew from the moment my house was blown away in a whirlwind and crushed the ugly hag next door that I had to find the great Warlock and ask him what to do, only to actually find a slimy green conman hiding behind a much larger shiny metallic conman! Take his robot, his home, his little dog too, and fling him in one of the four directions so far he doesn’t even know where he is! That should teach him a thing or two about ruining our dreams.”</t>
+  </si>
+  <si>
+    <t>*2. “I know how t-to p-p-punish him for all this lion,” stutters shaggy-haired friend of Borothy, Eek Ward. “W-w need a p-public execution. So no one ever dares t-to t-t-try a stunt like this again. T-think about it. He f-f-fed people’s hopes and dreams to the pigs, so we need them t-t-to eat his! Along with the r-rest of him. If we let p-pigs eat him alive, e-everyone will be t-too scared to tell a l-lie like that again! I w-would be, anyway...” [[color=blue]Must have Capital Punishment[/color]]</t>
+  </si>
+  <si>
+    <t>*3. “I know how t-to p-p-punish him for all this lion,” stutters shaggy-haired friend of Borothy, Eek Ward. “W-w need a p-public execution. So no one ever dares t-to t-t-try a stunt like this again. T-think about it. He f-f-fed people’s hopes and dreams to the pigs, so we need them t-t-to eat his! Along with the r-rest of him. If we let p-pigs eat him alive, e-everyone will be t-too scared to tell a l-lie like that again! I w-would be, anyway...” [[color=red]Must not have Capital Punishment[/color]]</t>
+  </si>
+  <si>
+    <t>4. “I can’t believe I fell for his lies!” shouts local farmer Scar Crown, who, you assume, is completely petrifying to pigeons. “I should’ve known from the get-go with how facetious his reasoning was. Sorry, fallacious! Logical fallacies! I mean honestly, I really should’ve put it together when the big guy started shouting ‘Error! Error!’ but I had assumed he only just realized he made the platypus! Anyway, we don’t have to be punitive here, and prevention is better than damage control. All we need to do is lobotomize him by sticking a good old ice pick up the tear duct, and then he’ll never be able to concoct a plan like this again! It’s genuine, I tell you! Sorry, genius.”</t>
+  </si>
+  <si>
+    <t>5. “No, no! I can’t believe all of you are buying into this!” protests conspiracy theorist and notably thin man [REDACTED], who refuses to tell anyone his real name for fear of Bigtopian assassins. After applying a fresh layer of duct tape to his foil hat, he continues, “The Great Warlock is being set up! Framed! And I know just by who. That Bigtopian hag, Glinder! Why, I bet she’s the reason Borothy’s house went flying in the first place! She used her witchcraft to sever his connection to the great one above, and made it look like he was just using some robot all along. If you have any heart, splash cold water on that witch’s plans and let this man go free!”</t>
+  </si>
+  <si>
+    <t>[b][anchor=1842]#1842[/anchor]: TBD[/b]</t>
+  </si>
+  <si>
+    <t>[b][anchor=1843]#1843[/anchor]: TBD[/b]</t>
+  </si>
+  <si>
+    <t>[b][anchor=1844]#1844[/anchor]: TBD[/b]</t>
+  </si>
+  <si>
+    <t>[b][anchor=1845]#1845[/anchor]: TBD[/b]</t>
+  </si>
+  <si>
+    <t>[b][anchor=1846]#1846[/anchor]: TBD[/b]</t>
+  </si>
+  <si>
+    <t>[b][anchor=1847]#1847[/anchor]: TBD[/b]</t>
+  </si>
+  <si>
+    <t>[b][anchor=1848]#1848[/anchor]: TBD[/b]</t>
+  </si>
+  <si>
+    <t>[b][anchor=1849]#1849[/anchor]: TBD[/b]</t>
+  </si>
+  <si>
+    <t>Bare the Builder</t>
+  </si>
+  <si>
+    <t>About Face</t>
+  </si>
+  <si>
+    <t>The God Illusion</t>
+  </si>
+  <si>
+    <t>Bare the Builder [United Calanworie; ed: Kractero]</t>
+  </si>
+  <si>
+    <t>About Face [Candlewhisper Archive; ed: Haymarket Riot]</t>
+  </si>
+  <si>
+    <t>The God Illusion [Varanius; ed: Haymarket Riot]</t>
   </si>
 </sst>
 </file>
@@ -1473,9 +1564,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -5298,8 +5390,8 @@
         <v>452</v>
       </c>
       <c r="D235" t="str">
-        <f t="shared" si="3"/>
-        <v>#1820: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1820]Whatever Happened to Saturday Night?[/url] [Haymarket Riot, Sapphica Sororitas; ed: Haymarket Riot]</v>
+        <f>"#"&amp;A235&amp;": [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#"&amp;A235&amp;"]"&amp;B235&amp;"[/url] "&amp;C235</f>
+        <v>#1820: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1820]Whatever Happened to Saturday Night?[/url] [Haymarket Riot, Sapphica Sororitas; ed: Haymarket Riot]</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5313,8 +5405,8 @@
         <v>453</v>
       </c>
       <c r="D236" t="str">
-        <f t="shared" si="3"/>
-        <v>#1821: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1821]A Dilemma of (Musical) Note[/url] [Starenia; ed: The Ankhalic Vaspriot]</v>
+        <f t="shared" ref="D236:D256" si="4">"#"&amp;A236&amp;": [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#"&amp;A236&amp;"]"&amp;B236&amp;"[/url] "&amp;C236</f>
+        <v>#1821: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1821]A Dilemma of (Musical) Note[/url] [Starenia; ed: The Ankhalic Vaspriot]</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5328,8 +5420,8 @@
         <v>454</v>
       </c>
       <c r="D237" t="str">
-        <f t="shared" si="3"/>
-        <v>#1822: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1822]ShortTok on the Clock[/url] [The Northern Glacial Borderlands; ed: Southland]</v>
+        <f t="shared" si="4"/>
+        <v>#1822: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1822]ShortTok on the Clock[/url] [The Northern Glacial Borderlands; ed: Southland]</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5343,8 +5435,8 @@
         <v>455</v>
       </c>
       <c r="D238" t="str">
-        <f t="shared" si="3"/>
-        <v>#1823: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1823]High Stakes In the Jungle[/url] [Northern Slatavia; ed: Ostrovskiy]</v>
+        <f t="shared" si="4"/>
+        <v>#1823: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1823]High Stakes In the Jungle[/url] [Northern Slatavia; ed: Ostrovskiy]</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5358,8 +5450,8 @@
         <v>456</v>
       </c>
       <c r="D239" t="str">
-        <f t="shared" si="3"/>
-        <v>#1824: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1824]A Great Swansong?[/url] [Chan Island; ed: Southland]</v>
+        <f t="shared" si="4"/>
+        <v>#1824: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1824]A Great Swansong?[/url] [Chan Island; ed: Southland]</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5373,8 +5465,8 @@
         <v>457</v>
       </c>
       <c r="D240" t="str">
-        <f t="shared" si="3"/>
-        <v>#1825: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1825]Fish Out of Water[/url] [Westinor; ed: Southland]</v>
+        <f t="shared" si="4"/>
+        <v>#1825: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1825]Fish Out of Water[/url] [Westinor; ed: Southland]</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5388,8 +5480,8 @@
         <v>458</v>
       </c>
       <c r="D241" t="str">
-        <f t="shared" si="3"/>
-        <v>#1826: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1826]Cyclist? More Like Cycle-Pest![/url] [Markanite; ed: The Ankhalic Vaspriot]</v>
+        <f t="shared" si="4"/>
+        <v>#1826: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1826]Cyclist? More Like Cycle-Pest![/url] [Markanite; ed: The Ankhalic Vaspriot]</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5403,8 +5495,8 @@
         <v>459</v>
       </c>
       <c r="D242" t="str">
-        <f t="shared" si="3"/>
-        <v>#1827: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1827]Row, Row, Row Your Drug Boat![/url] [Burg Land; ed: Kractero]</v>
+        <f t="shared" si="4"/>
+        <v>#1827: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1827]Row, Row, Row Your Drug Boat![/url] [Burg Land; ed: Kractero]</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5418,8 +5510,8 @@
         <v>460</v>
       </c>
       <c r="D243" t="str">
-        <f t="shared" si="3"/>
-        <v>#1828: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1828]A Dole-ful Gamble[/url] [Giovanniland; ed: Kractero]</v>
+        <f t="shared" si="4"/>
+        <v>#1828: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1828]A Dole-ful Gamble[/url] [Giovanniland; ed: Kractero]</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5433,8 +5525,8 @@
         <v>399</v>
       </c>
       <c r="D244" t="str">
-        <f t="shared" si="3"/>
-        <v>#1829: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1829]Fly on the Wall Diplomacy[/url] [Fhaengshia; ed: Haymarket Riot]</v>
+        <f t="shared" si="4"/>
+        <v>#1829: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1829]Fly on the Wall Diplomacy[/url] [Fhaengshia; ed: Haymarket Riot]</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5448,8 +5540,8 @@
         <v>191</v>
       </c>
       <c r="D245" t="str">
-        <f t="shared" si="3"/>
-        <v>#1830: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1830]You Wouldn’t Download Segregation[/url] [Raionitu; ed: Raionitu]</v>
+        <f t="shared" si="4"/>
+        <v>#1830: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1830]You Wouldn’t Download Segregation[/url] [Raionitu; ed: Raionitu]</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5463,8 +5555,8 @@
         <v>336</v>
       </c>
       <c r="D246" t="str">
-        <f t="shared" si="3"/>
-        <v>#1831: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1831]Some @@DEMONYM_NOUN_PLURAL@@ May Die[/url] [Haymarket Riot; ed: Haymarket Riot]</v>
+        <f t="shared" si="4"/>
+        <v>#1831: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1831]Some @@DEMONYM_NOUN_PLURAL@@ May Die[/url] [Haymarket Riot; ed: Haymarket Riot]</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5478,8 +5570,8 @@
         <v>171</v>
       </c>
       <c r="D247" t="str">
-        <f t="shared" si="3"/>
-        <v>#1832: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1832]À La Cartel[/url] [The Ankhalic Vaspriot; ed: The Ankhalic Vaspriot]</v>
+        <f t="shared" si="4"/>
+        <v>#1832: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1832]À La Cartel[/url] [The Ankhalic Vaspriot; ed: The Ankhalic Vaspriot]</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5493,8 +5585,8 @@
         <v>461</v>
       </c>
       <c r="D248" t="str">
-        <f t="shared" si="3"/>
-        <v>#1833: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1833]Patron Sinner[/url] [The Free Joy State; ed: Nardin]</v>
+        <f t="shared" si="4"/>
+        <v>#1833: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1833]Patron Sinner[/url] [The Free Joy State; ed: Nardin]</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5508,8 +5600,8 @@
         <v>467</v>
       </c>
       <c r="D249" t="str">
-        <f t="shared" si="3"/>
-        <v>#1834: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1834]Trams-phobic[/url] [Lavrada; ed: Haymarket Riot &amp; Southland]</v>
+        <f t="shared" si="4"/>
+        <v>#1834: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1834]Trams-phobic[/url] [Lavrada; ed: Haymarket Riot &amp; Southland]</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5523,8 +5615,8 @@
         <v>468</v>
       </c>
       <c r="D250" t="str">
-        <f t="shared" si="3"/>
-        <v>#1835: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1835]Potatoes in Hot Water[/url] [Stevist Guam; ed: Kaschovia]</v>
+        <f t="shared" si="4"/>
+        <v>#1835: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1835]Potatoes in Hot Water[/url] [Stevist Guam; ed: Kaschovia]</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5538,8 +5630,8 @@
         <v>469</v>
       </c>
       <c r="D251" t="str">
-        <f t="shared" si="3"/>
-        <v>#1836: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1836]Tummy Troubles[/url] [Buceroque; ed: Nardin]</v>
+        <f t="shared" si="4"/>
+        <v>#1836: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1836]Tummy Troubles[/url] [Buceroque; ed: Nardin]</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5553,8 +5645,8 @@
         <v>470</v>
       </c>
       <c r="D252" t="str">
-        <f t="shared" si="3"/>
-        <v>#1837: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1837]Sue That Storm[/url] [Roman Garcia; ed: Raionitu]</v>
+        <f t="shared" si="4"/>
+        <v>#1837: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1837]Sue That Storm[/url] [Roman Garcia; ed: Raionitu]</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5568,23 +5660,53 @@
         <v>471</v>
       </c>
       <c r="D253" t="str">
-        <f t="shared" si="3"/>
-        <v>#1838: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1838]Who’s Afraid of Red, Yellow, and Blue?[/url] [The Ankhalic Vaspriot; ed: Jiangbei]</v>
+        <f t="shared" si="4"/>
+        <v>#1838: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1838]Who’s Afraid of Red, Yellow, and Blue?[/url] [The Ankhalic Vaspriot; ed: Jiangbei]</v>
       </c>
     </row>
     <row r="254" spans="1:4">
       <c r="A254">
         <v>1839</v>
       </c>
+      <c r="B254" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D254" t="str">
+        <f t="shared" si="4"/>
+        <v>#1839: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1839]Bare the Builder[/url] Bare the Builder [United Calanworie; ed: Kractero]</v>
+      </c>
     </row>
     <row r="255" spans="1:4">
       <c r="A255">
         <v>1840</v>
       </c>
+      <c r="B255" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D255" t="str">
+        <f t="shared" si="4"/>
+        <v>#1840: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1840]About Face[/url] About Face [Candlewhisper Archive; ed: Haymarket Riot]</v>
+      </c>
     </row>
     <row r="256" spans="1:4">
       <c r="A256">
         <v>1841</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="D256" t="str">
+        <f t="shared" si="4"/>
+        <v>#1841: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1841]The God Illusion[/url] The God Illusion [Varanius; ed: Haymarket Riot]</v>
       </c>
     </row>
     <row r="257" spans="1:1">
@@ -5867,4 +5989,191 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.35"/>
+  <cols>
+    <col min="1" max="1" width="105.9375" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="10.8203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A1:A59">
+    <sortCondition ref="A1"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Issues Section Template.xlsx
+++ b/Issues Section Template.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="267" yWindow="93" windowWidth="13720" windowHeight="5233"/>
@@ -12,12 +12,12 @@
     <sheet name="Blad3" sheetId="3" r:id="rId3"/>
     <sheet name="Tabelle1" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="125725" refMode="R1C1"/>
+  <calcPr calcId="124519" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="523">
   <si>
     <t>[The Free Joy State; ed: Candlewhisper Archive]</t>
   </si>
@@ -1516,13 +1516,76 @@
     <t>The God Illusion</t>
   </si>
   <si>
-    <t>Bare the Builder [United Calanworie; ed: Kractero]</t>
-  </si>
-  <si>
-    <t>About Face [Candlewhisper Archive; ed: Haymarket Riot]</t>
-  </si>
-  <si>
-    <t>The God Illusion [Varanius; ed: Haymarket Riot]</t>
+    <t>[United Calanworie; ed: Kractero]</t>
+  </si>
+  <si>
+    <t>[Varanius; ed: Haymarket Riot]</t>
+  </si>
+  <si>
+    <t>Dead Men Walking</t>
+  </si>
+  <si>
+    <t>[Chan Island; ed: Kractero]</t>
+  </si>
+  <si>
+    <t>The Phony Lisa</t>
+  </si>
+  <si>
+    <t>[Second Best Card Collector; ed: Southland]</t>
+  </si>
+  <si>
+    <t>A Spicy Situation</t>
+  </si>
+  <si>
+    <t>[Jiangbei; ed: The Marsupial Illuminati]</t>
+  </si>
+  <si>
+    <t>Pop Goes the Girl Group</t>
+  </si>
+  <si>
+    <t>[Thorn1000; ed: Pogaria]</t>
+  </si>
+  <si>
+    <t>New Dental Research Hard to Chew</t>
+  </si>
+  <si>
+    <t>[Agnagina; ed: The Ankhalic Vaspriot]</t>
+  </si>
+  <si>
+    <t>A Rhetorical Question</t>
+  </si>
+  <si>
+    <t>[Azure Mines; ed: The Ankhalic Vaspriot]</t>
+  </si>
+  <si>
+    <t>Man (F)or Machine?</t>
+  </si>
+  <si>
+    <t>[Arma tulharia; ed: Nardin]</t>
+  </si>
+  <si>
+    <t>On the Bubble</t>
+  </si>
+  <si>
+    <t>[Thorn1000 &amp; Valoptia; ed: Thorn1000]</t>
+  </si>
+  <si>
+    <t>Explosive Conflict</t>
+  </si>
+  <si>
+    <t>[Cretox State; ed: The Ankhalic Vaspriot]</t>
+  </si>
+  <si>
+    <t>Rally 'Round the Flag</t>
+  </si>
+  <si>
+    <t>[Dushina, Pathonia; ed: Ostrovskiy]</t>
+  </si>
+  <si>
+    <t>A Question of Pride</t>
+  </si>
+  <si>
+    <t>A Whole New World</t>
   </si>
 </sst>
 </file>
@@ -1564,10 +1627,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1863,7 +1927,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D270"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.9375" defaultRowHeight="14.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.35"/>
   <cols>
     <col min="1" max="1" width="9.8203125" customWidth="1"/>
     <col min="2" max="2" width="32.76171875" customWidth="1"/>
@@ -4763,7 +4827,7 @@
         <v>223</v>
       </c>
       <c r="D193" t="str">
-        <f t="shared" ref="D193:D253" si="3">"#"&amp;A193&amp;": [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#"&amp;A193&amp;"]"&amp;B193&amp;"[/url] "&amp;C193</f>
+        <f t="shared" ref="D193:D234" si="3">"#"&amp;A193&amp;": [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#"&amp;A193&amp;"]"&amp;B193&amp;"[/url] "&amp;C193</f>
         <v>#1778: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=75#1778]Milk Made[/url] [Candlewhisper Archive; ed: Bisofeyr]</v>
       </c>
     </row>
@@ -5405,7 +5469,7 @@
         <v>453</v>
       </c>
       <c r="D236" t="str">
-        <f t="shared" ref="D236:D256" si="4">"#"&amp;A236&amp;": [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#"&amp;A236&amp;"]"&amp;B236&amp;"[/url] "&amp;C236</f>
+        <f t="shared" ref="D236:D268" si="4">"#"&amp;A236&amp;": [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#"&amp;A236&amp;"]"&amp;B236&amp;"[/url] "&amp;C236</f>
         <v>#1821: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1821]A Dilemma of (Musical) Note[/url] [Starenia; ed: The Ankhalic Vaspriot]</v>
       </c>
     </row>
@@ -5676,7 +5740,7 @@
       </c>
       <c r="D254" t="str">
         <f t="shared" si="4"/>
-        <v>#1839: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1839]Bare the Builder[/url] Bare the Builder [United Calanworie; ed: Kractero]</v>
+        <v>#1839: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1839]Bare the Builder[/url] [United Calanworie; ed: Kractero]</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5687,11 +5751,11 @@
         <v>497</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>500</v>
+        <v>347</v>
       </c>
       <c r="D255" t="str">
         <f t="shared" si="4"/>
-        <v>#1840: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1840]About Face[/url] About Face [Candlewhisper Archive; ed: Haymarket Riot]</v>
+        <v>#1840: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1840]About Face[/url] [Candlewhisper Archive; ed: Haymarket Riot]</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5702,79 +5766,199 @@
         <v>498</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D256" t="str">
         <f t="shared" si="4"/>
-        <v>#1841: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1841]The God Illusion[/url] The God Illusion [Varanius; ed: Haymarket Riot]</v>
-      </c>
-    </row>
-    <row r="257" spans="1:1">
-      <c r="A257">
+        <v>#1841: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1841]The God Illusion[/url] [Varanius; ed: Haymarket Riot]</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" s="1">
         <v>1842</v>
       </c>
-    </row>
-    <row r="258" spans="1:1">
+      <c r="B257" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="D257" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>#1842: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1842]Dead Men Walking[/url] [Chan Island; ed: Kractero]</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
       <c r="A258">
         <v>1843</v>
       </c>
-    </row>
-    <row r="259" spans="1:1">
+      <c r="B258" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C258" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="D258" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>#1843: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1843]The Phony Lisa[/url] [Second Best Card Collector; ed: Southland]</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
       <c r="A259">
         <v>1844</v>
       </c>
-    </row>
-    <row r="260" spans="1:1">
+      <c r="B259" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D259" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>#1844: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1844]A Spicy Situation[/url] [Jiangbei; ed: The Marsupial Illuminati]</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
       <c r="A260">
         <v>1845</v>
       </c>
-    </row>
-    <row r="261" spans="1:1">
+      <c r="B260" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="D260" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>#1845: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1845]Pop Goes the Girl Group[/url] [Thorn1000; ed: Pogaria]</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
       <c r="A261">
         <v>1846</v>
       </c>
-    </row>
-    <row r="262" spans="1:1">
+      <c r="B261" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="D261" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>#1846: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1846]New Dental Research Hard to Chew[/url] [Agnagina; ed: The Ankhalic Vaspriot]</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
       <c r="A262">
         <v>1847</v>
       </c>
-    </row>
-    <row r="263" spans="1:1">
+      <c r="B262" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="C262" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D262" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>#1847: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1847]A Rhetorical Question[/url] [Azure Mines; ed: The Ankhalic Vaspriot]</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
       <c r="A263">
         <v>1848</v>
       </c>
-    </row>
-    <row r="264" spans="1:1">
+      <c r="B263" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="C263" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D263" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>#1848: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1848]Man (F)or Machine?[/url] [Arma tulharia; ed: Nardin]</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
       <c r="A264">
         <v>1849</v>
       </c>
-    </row>
-    <row r="265" spans="1:1">
+      <c r="B264" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C264" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="D264" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>#1849: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1849]On the Bubble[/url] [Thorn1000 &amp; Valoptia; ed: Thorn1000]</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
       <c r="A265">
         <v>1850</v>
       </c>
-    </row>
-    <row r="266" spans="1:1">
+      <c r="B265" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="D265" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>#1850: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1850]Explosive Conflict[/url] [Cretox State; ed: The Ankhalic Vaspriot]</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
       <c r="A266">
         <v>1851</v>
       </c>
-    </row>
-    <row r="267" spans="1:1">
+      <c r="B266" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="D266" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>#1851: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1851]Rally 'Round the Flag[/url] [Dushina, Pathonia; ed: Ostrovskiy]</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
       <c r="A267">
         <v>1852</v>
       </c>
-    </row>
-    <row r="268" spans="1:1">
+      <c r="B267" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D267" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>#1852: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1852]A Question of Pride[/url] [Candlewhisper Archive; ed: Bisofeyr]</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
       <c r="A268">
         <v>1853</v>
       </c>
-    </row>
-    <row r="269" spans="1:1">
+      <c r="B268" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D268" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>#1853: [url=http://forum.nationstates.net/viewtopic.php?f=13&amp;t=88&amp;start=100#1853]A Whole New World[/url] [Southland; ed: Southland]</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
       <c r="A269">
         <v>1854</v>
       </c>
     </row>
-    <row r="270" spans="1:1">
+    <row r="270" spans="1:4">
       <c r="A270">
         <v>1855</v>
       </c>
